--- a/shared/planilla_mes/planilla_2026-06.xlsx
+++ b/shared/planilla_mes/planilla_2026-06.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U576"/>
+  <dimension ref="A1:U577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -33645,7 +33645,7 @@
       </c>
       <c r="C509" s="8" t="inlineStr">
         <is>
-          <t>NELY MORENO LICITA</t>
+          <t>NELLY MORENO LICITO</t>
         </is>
       </c>
       <c r="D509" s="7" t="inlineStr">
@@ -38051,6 +38051,71 @@
       <c r="S576" s="13" t="n"/>
       <c r="T576" s="14" t="n"/>
       <c r="U576" s="15" t="n"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="7" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B577" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C577" s="8" t="inlineStr">
+        <is>
+          <t>NELLY MORENO LICITO</t>
+        </is>
+      </c>
+      <c r="D577" s="7" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E577" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F577" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G577" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H577" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I577" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J577" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K577" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L577" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M577" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N577" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O577" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P577" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q577" s="12" t="n">
+        <v>113</v>
+      </c>
+      <c r="R577" s="13" t="n"/>
+      <c r="S577" s="13" t="n"/>
+      <c r="T577" s="14" t="n"/>
+      <c r="U577" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/shared/planilla_mes/planilla_2026-06.xlsx
+++ b/shared/planilla_mes/planilla_2026-06.xlsx
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R3" s="13" t="n"/>
       <c r="S3" s="13" t="n"/>
@@ -865,7 +865,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="12" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R4" s="13" t="n"/>
       <c r="S4" s="13" t="n"/>
@@ -930,7 +930,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R5" s="13" t="n"/>
       <c r="S5" s="13" t="n"/>
@@ -995,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="R6" s="13" t="n"/>
       <c r="S6" s="13" t="n"/>
@@ -1060,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="R7" s="13" t="n"/>
       <c r="S7" s="13" t="n"/>
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="R8" s="13" t="n"/>
       <c r="S8" s="13" t="n"/>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="R9" s="13" t="n"/>
       <c r="S9" s="13" t="n"/>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="R10" s="13" t="n"/>
       <c r="S10" s="13" t="n"/>
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="R11" s="13" t="n"/>
       <c r="S11" s="13" t="n"/>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R12" s="13" t="n"/>
       <c r="S12" s="13" t="n"/>
@@ -1432,7 +1432,7 @@
         <v>8</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L13" s="10" t="n">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="R13" s="13" t="n"/>
       <c r="S13" s="13" t="n"/>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R14" s="13" t="n"/>
       <c r="S14" s="13" t="n"/>
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R15" s="13" t="n"/>
       <c r="S15" s="13" t="n"/>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R16" s="13" t="n"/>
       <c r="S16" s="13" t="n"/>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R17" s="13" t="n"/>
       <c r="S17" s="13" t="n"/>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="R18" s="13" t="n"/>
       <c r="S18" s="13" t="n"/>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="R19" s="13" t="n"/>
       <c r="S19" s="13" t="n"/>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="R20" s="13" t="n"/>
       <c r="S20" s="13" t="n"/>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R21" s="13" t="n"/>
       <c r="S21" s="13" t="n"/>
@@ -2035,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R22" s="13" t="n"/>
       <c r="S22" s="13" t="n"/>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R23" s="13" t="n"/>
       <c r="S23" s="13" t="n"/>
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="R24" s="13" t="n"/>
       <c r="S24" s="13" t="n"/>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R25" s="13" t="n"/>
       <c r="S25" s="13" t="n"/>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="R26" s="13" t="n"/>
       <c r="S26" s="13" t="n"/>
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R27" s="13" t="n"/>
       <c r="S27" s="13" t="n"/>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="R28" s="13" t="n"/>
       <c r="S28" s="13" t="n"/>
@@ -2490,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R29" s="13" t="n"/>
       <c r="S29" s="13" t="n"/>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R30" s="13" t="n"/>
       <c r="S30" s="13" t="n"/>
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="R31" s="13" t="n"/>
       <c r="S31" s="13" t="n"/>
@@ -2685,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="R32" s="13" t="n"/>
       <c r="S32" s="13" t="n"/>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R33" s="13" t="n"/>
       <c r="S33" s="13" t="n"/>
@@ -2815,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="R34" s="13" t="n"/>
       <c r="S34" s="13" t="n"/>
@@ -2880,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="R35" s="13" t="n"/>
       <c r="S35" s="13" t="n"/>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="R36" s="13" t="n"/>
       <c r="S36" s="13" t="n"/>
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R37" s="13" t="n"/>
       <c r="S37" s="13" t="n"/>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="R38" s="13" t="n"/>
       <c r="S38" s="13" t="n"/>
@@ -3140,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="R39" s="13" t="n"/>
       <c r="S39" s="13" t="n"/>
@@ -3205,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>353</v>
+        <v>0</v>
       </c>
       <c r="R40" s="13" t="n"/>
       <c r="S40" s="13" t="n"/>
@@ -3270,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R41" s="13" t="n"/>
       <c r="S41" s="13" t="n"/>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="R42" s="13" t="n"/>
       <c r="S42" s="13" t="n"/>
@@ -3400,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="R43" s="13" t="n"/>
       <c r="S43" s="13" t="n"/>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="R44" s="13" t="n"/>
       <c r="S44" s="13" t="n"/>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="R45" s="13" t="n"/>
       <c r="S45" s="13" t="n"/>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R46" s="13" t="n"/>
       <c r="S46" s="13" t="n"/>
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="R47" s="13" t="n"/>
       <c r="S47" s="13" t="n"/>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R48" s="13" t="n"/>
       <c r="S48" s="13" t="n"/>
@@ -3790,7 +3790,7 @@
         <v>0</v>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="R49" s="13" t="n"/>
       <c r="S49" s="13" t="n"/>
@@ -3855,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R50" s="13" t="n"/>
       <c r="S50" s="13" t="n"/>
@@ -3920,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R51" s="13" t="n"/>
       <c r="S51" s="13" t="n"/>
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="R52" s="13" t="n"/>
       <c r="S52" s="13" t="n"/>
@@ -4050,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="R53" s="13" t="n"/>
       <c r="S53" s="13" t="n"/>
@@ -4115,7 +4115,7 @@
         <v>0</v>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R54" s="13" t="n"/>
       <c r="S54" s="13" t="n"/>
@@ -4180,7 +4180,7 @@
         <v>0</v>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R55" s="13" t="n"/>
       <c r="S55" s="13" t="n"/>
@@ -4245,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="R56" s="13" t="n"/>
       <c r="S56" s="13" t="n"/>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="R57" s="13" t="n"/>
       <c r="S57" s="13" t="n"/>
@@ -4375,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="R58" s="13" t="n"/>
       <c r="S58" s="13" t="n"/>
@@ -4440,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="Q59" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="R59" s="13" t="n"/>
       <c r="S59" s="13" t="n"/>
@@ -4505,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="Q60" s="12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R60" s="13" t="n"/>
       <c r="S60" s="13" t="n"/>
@@ -4570,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R61" s="13" t="n"/>
       <c r="S61" s="13" t="n"/>
@@ -4635,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="R62" s="13" t="n"/>
       <c r="S62" s="13" t="n"/>
@@ -4700,7 +4700,7 @@
         <v>0</v>
       </c>
       <c r="Q63" s="12" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="R63" s="13" t="n"/>
       <c r="S63" s="13" t="n"/>
@@ -4765,7 +4765,7 @@
         <v>0</v>
       </c>
       <c r="Q64" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R64" s="13" t="n"/>
       <c r="S64" s="13" t="n"/>
@@ -4830,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="Q65" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R65" s="13" t="n"/>
       <c r="S65" s="13" t="n"/>
@@ -4877,13 +4877,13 @@
         <v>29</v>
       </c>
       <c r="K66" s="10" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L66" s="10" t="n">
         <v>25</v>
       </c>
       <c r="M66" s="10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N66" s="10" t="n">
         <v>0</v>
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="Q66" s="12" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="R66" s="13" t="n"/>
       <c r="S66" s="13" t="n"/>
@@ -4960,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="Q67" s="12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="R67" s="13" t="n"/>
       <c r="S67" s="13" t="n"/>
@@ -5007,7 +5007,7 @@
         <v>17</v>
       </c>
       <c r="K68" s="10" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L68" s="10" t="n">
         <v>0</v>
@@ -5025,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="Q68" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="R68" s="13" t="n"/>
       <c r="S68" s="13" t="n"/>
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="Q69" s="12" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="R69" s="13" t="n"/>
       <c r="S69" s="13" t="n"/>
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="Q70" s="12" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="R70" s="13" t="n"/>
       <c r="S70" s="13" t="n"/>
@@ -5220,7 +5220,7 @@
         <v>0</v>
       </c>
       <c r="Q71" s="12" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="R71" s="13" t="n"/>
       <c r="S71" s="13" t="n"/>
@@ -5285,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="Q72" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="R72" s="13" t="n"/>
       <c r="S72" s="13" t="n"/>
@@ -5350,7 +5350,7 @@
         <v>0</v>
       </c>
       <c r="Q73" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R73" s="13" t="n"/>
       <c r="S73" s="13" t="n"/>
@@ -5415,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="Q74" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R74" s="13" t="n"/>
       <c r="S74" s="13" t="n"/>
@@ -5480,7 +5480,7 @@
         <v>0</v>
       </c>
       <c r="Q75" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R75" s="13" t="n"/>
       <c r="S75" s="13" t="n"/>
@@ -5545,7 +5545,7 @@
         <v>0</v>
       </c>
       <c r="Q76" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R76" s="13" t="n"/>
       <c r="S76" s="13" t="n"/>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="Q77" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R77" s="13" t="n"/>
       <c r="S77" s="13" t="n"/>
@@ -5675,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="Q78" s="12" t="n">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="R78" s="13" t="n"/>
       <c r="S78" s="13" t="n"/>
@@ -5740,7 +5740,7 @@
         <v>0</v>
       </c>
       <c r="Q79" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="R79" s="13" t="n"/>
       <c r="S79" s="13" t="n"/>
@@ -5784,7 +5784,7 @@
         <v>3</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K80" s="10" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         <v>0</v>
       </c>
       <c r="Q80" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="R80" s="13" t="n"/>
       <c r="S80" s="13" t="n"/>
@@ -5870,7 +5870,7 @@
         <v>0</v>
       </c>
       <c r="Q81" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R81" s="13" t="n"/>
       <c r="S81" s="13" t="n"/>
@@ -5917,7 +5917,7 @@
         <v>8</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L82" s="10" t="n">
         <v>346</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="Q82" s="12" t="n">
-        <v>362</v>
+        <v>0</v>
       </c>
       <c r="R82" s="13" t="n"/>
       <c r="S82" s="13" t="n"/>
@@ -6000,7 +6000,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="R83" s="13" t="n"/>
       <c r="S83" s="13" t="n"/>
@@ -6065,7 +6065,7 @@
         <v>0</v>
       </c>
       <c r="Q84" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="R84" s="13" t="n"/>
       <c r="S84" s="13" t="n"/>
@@ -6130,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="Q85" s="12" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="R85" s="13" t="n"/>
       <c r="S85" s="13" t="n"/>
@@ -6195,7 +6195,7 @@
         <v>0</v>
       </c>
       <c r="Q86" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="R86" s="13" t="n"/>
       <c r="S86" s="13" t="n"/>
@@ -6260,7 +6260,7 @@
         <v>0</v>
       </c>
       <c r="Q87" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R87" s="13" t="n"/>
       <c r="S87" s="13" t="n"/>
@@ -6325,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="Q88" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="R88" s="13" t="n"/>
       <c r="S88" s="13" t="n"/>
@@ -6390,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="Q89" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R89" s="13" t="n"/>
       <c r="S89" s="13" t="n"/>
@@ -6455,7 +6455,7 @@
         <v>0</v>
       </c>
       <c r="Q90" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R90" s="13" t="n"/>
       <c r="S90" s="13" t="n"/>
@@ -6499,7 +6499,7 @@
         <v>3</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K91" s="10" t="n">
         <v>0</v>
@@ -6520,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="Q91" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="R91" s="13" t="n"/>
       <c r="S91" s="13" t="n"/>
@@ -6585,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="Q92" s="12" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="R92" s="13" t="n"/>
       <c r="S92" s="13" t="n"/>
@@ -6650,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="Q93" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="R93" s="13" t="n"/>
       <c r="S93" s="13" t="n"/>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="12" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="R94" s="13" t="n"/>
       <c r="S94" s="13" t="n"/>
@@ -6780,7 +6780,7 @@
         <v>0</v>
       </c>
       <c r="Q95" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R95" s="13" t="n"/>
       <c r="S95" s="13" t="n"/>
@@ -6845,7 +6845,7 @@
         <v>0</v>
       </c>
       <c r="Q96" s="12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R96" s="13" t="n"/>
       <c r="S96" s="13" t="n"/>
@@ -6910,7 +6910,7 @@
         <v>0</v>
       </c>
       <c r="Q97" s="12" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="R97" s="13" t="n"/>
       <c r="S97" s="13" t="n"/>
@@ -6963,7 +6963,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N98" s="10" t="n">
         <v>0</v>
@@ -6975,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="Q98" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R98" s="13" t="n"/>
       <c r="S98" s="13" t="n"/>
@@ -7040,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="Q99" s="12" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="R99" s="13" t="n"/>
       <c r="S99" s="13" t="n"/>
@@ -7105,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="Q100" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="R100" s="13" t="n"/>
       <c r="S100" s="13" t="n"/>
@@ -7170,7 +7170,7 @@
         <v>0</v>
       </c>
       <c r="Q101" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R101" s="13" t="n"/>
       <c r="S101" s="13" t="n"/>
@@ -7235,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="Q102" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R102" s="13" t="n"/>
       <c r="S102" s="13" t="n"/>
@@ -7300,7 +7300,7 @@
         <v>0</v>
       </c>
       <c r="Q103" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R103" s="13" t="n"/>
       <c r="S103" s="13" t="n"/>
@@ -7365,7 +7365,7 @@
         <v>0</v>
       </c>
       <c r="Q104" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R104" s="13" t="n"/>
       <c r="S104" s="13" t="n"/>
@@ -7430,7 +7430,7 @@
         <v>0</v>
       </c>
       <c r="Q105" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R105" s="13" t="n"/>
       <c r="S105" s="13" t="n"/>
@@ -7495,7 +7495,7 @@
         <v>0</v>
       </c>
       <c r="Q106" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R106" s="13" t="n"/>
       <c r="S106" s="13" t="n"/>
@@ -7560,7 +7560,7 @@
         <v>0</v>
       </c>
       <c r="Q107" s="12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R107" s="13" t="n"/>
       <c r="S107" s="13" t="n"/>
@@ -7625,7 +7625,7 @@
         <v>0</v>
       </c>
       <c r="Q108" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R108" s="13" t="n"/>
       <c r="S108" s="13" t="n"/>
@@ -7690,7 +7690,7 @@
         <v>0</v>
       </c>
       <c r="Q109" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R109" s="13" t="n"/>
       <c r="S109" s="13" t="n"/>
@@ -7755,7 +7755,7 @@
         <v>0</v>
       </c>
       <c r="Q110" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R110" s="13" t="n"/>
       <c r="S110" s="13" t="n"/>
@@ -7820,7 +7820,7 @@
         <v>0</v>
       </c>
       <c r="Q111" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R111" s="13" t="n"/>
       <c r="S111" s="13" t="n"/>
@@ -7885,7 +7885,7 @@
         <v>0</v>
       </c>
       <c r="Q112" s="12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R112" s="13" t="n"/>
       <c r="S112" s="13" t="n"/>
@@ -7950,7 +7950,7 @@
         <v>0</v>
       </c>
       <c r="Q113" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R113" s="13" t="n"/>
       <c r="S113" s="13" t="n"/>
@@ -8015,7 +8015,7 @@
         <v>0</v>
       </c>
       <c r="Q114" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R114" s="13" t="n"/>
       <c r="S114" s="13" t="n"/>
@@ -8080,7 +8080,7 @@
         <v>0</v>
       </c>
       <c r="Q115" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R115" s="13" t="n"/>
       <c r="S115" s="13" t="n"/>
@@ -8145,7 +8145,7 @@
         <v>0</v>
       </c>
       <c r="Q116" s="12" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R116" s="13" t="n"/>
       <c r="S116" s="13" t="n"/>
@@ -8210,7 +8210,7 @@
         <v>0</v>
       </c>
       <c r="Q117" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="R117" s="13" t="n"/>
       <c r="S117" s="13" t="n"/>
@@ -8275,7 +8275,7 @@
         <v>0</v>
       </c>
       <c r="Q118" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R118" s="13" t="n"/>
       <c r="S118" s="13" t="n"/>
@@ -8340,7 +8340,7 @@
         <v>0</v>
       </c>
       <c r="Q119" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R119" s="13" t="n"/>
       <c r="S119" s="13" t="n"/>
@@ -8405,7 +8405,7 @@
         <v>0</v>
       </c>
       <c r="Q120" s="12" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="R120" s="13" t="n"/>
       <c r="S120" s="13" t="n"/>
@@ -8470,7 +8470,7 @@
         <v>0</v>
       </c>
       <c r="Q121" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="R121" s="13" t="n"/>
       <c r="S121" s="13" t="n"/>
@@ -8535,7 +8535,7 @@
         <v>0</v>
       </c>
       <c r="Q122" s="12" t="n">
-        <v>48.5</v>
+        <v>0</v>
       </c>
       <c r="R122" s="13" t="n"/>
       <c r="S122" s="13" t="n"/>
@@ -8588,7 +8588,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N123" s="10" t="n">
         <v>0</v>
@@ -8600,7 +8600,7 @@
         <v>0</v>
       </c>
       <c r="Q123" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R123" s="13" t="n"/>
       <c r="S123" s="13" t="n"/>
@@ -8665,7 +8665,7 @@
         <v>0</v>
       </c>
       <c r="Q124" s="12" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="R124" s="13" t="n"/>
       <c r="S124" s="13" t="n"/>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="Q125" s="12" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="R125" s="13" t="n"/>
       <c r="S125" s="13" t="n"/>
@@ -8795,7 +8795,7 @@
         <v>0</v>
       </c>
       <c r="Q126" s="12" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="R126" s="13" t="n"/>
       <c r="S126" s="13" t="n"/>
@@ -8860,7 +8860,7 @@
         <v>0</v>
       </c>
       <c r="Q127" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R127" s="13" t="n"/>
       <c r="S127" s="13" t="n"/>
@@ -8925,7 +8925,7 @@
         <v>0</v>
       </c>
       <c r="Q128" s="12" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="R128" s="13" t="n"/>
       <c r="S128" s="13" t="n"/>
@@ -8990,7 +8990,7 @@
         <v>0</v>
       </c>
       <c r="Q129" s="12" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="R129" s="13" t="n"/>
       <c r="S129" s="13" t="n"/>
@@ -9055,7 +9055,7 @@
         <v>0</v>
       </c>
       <c r="Q130" s="12" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="R130" s="13" t="n"/>
       <c r="S130" s="13" t="n"/>
@@ -9120,7 +9120,7 @@
         <v>0</v>
       </c>
       <c r="Q131" s="12" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="R131" s="13" t="n"/>
       <c r="S131" s="13" t="n"/>
@@ -9185,7 +9185,7 @@
         <v>0</v>
       </c>
       <c r="Q132" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R132" s="13" t="n"/>
       <c r="S132" s="13" t="n"/>
@@ -9250,7 +9250,7 @@
         <v>0</v>
       </c>
       <c r="Q133" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R133" s="13" t="n"/>
       <c r="S133" s="13" t="n"/>
@@ -9315,7 +9315,7 @@
         <v>0</v>
       </c>
       <c r="Q134" s="12" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="R134" s="13" t="n"/>
       <c r="S134" s="13" t="n"/>
@@ -9380,7 +9380,7 @@
         <v>0</v>
       </c>
       <c r="Q135" s="12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="R135" s="13" t="n"/>
       <c r="S135" s="13" t="n"/>
@@ -9445,7 +9445,7 @@
         <v>0</v>
       </c>
       <c r="Q136" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="R136" s="13" t="n"/>
       <c r="S136" s="13" t="n"/>
@@ -9510,7 +9510,7 @@
         <v>0</v>
       </c>
       <c r="Q137" s="12" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="R137" s="13" t="n"/>
       <c r="S137" s="13" t="n"/>
@@ -9575,7 +9575,7 @@
         <v>0</v>
       </c>
       <c r="Q138" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R138" s="13" t="n"/>
       <c r="S138" s="13" t="n"/>
@@ -9640,7 +9640,7 @@
         <v>0</v>
       </c>
       <c r="Q139" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="R139" s="13" t="n"/>
       <c r="S139" s="13" t="n"/>
@@ -9705,7 +9705,7 @@
         <v>0</v>
       </c>
       <c r="Q140" s="12" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="R140" s="13" t="n"/>
       <c r="S140" s="13" t="n"/>
@@ -9770,7 +9770,7 @@
         <v>0</v>
       </c>
       <c r="Q141" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R141" s="13" t="n"/>
       <c r="S141" s="13" t="n"/>
@@ -9835,7 +9835,7 @@
         <v>0</v>
       </c>
       <c r="Q142" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R142" s="13" t="n"/>
       <c r="S142" s="13" t="n"/>
@@ -9900,7 +9900,7 @@
         <v>0</v>
       </c>
       <c r="Q143" s="12" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="R143" s="13" t="n"/>
       <c r="S143" s="13" t="n"/>
@@ -9965,7 +9965,7 @@
         <v>0</v>
       </c>
       <c r="Q144" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R144" s="13" t="n"/>
       <c r="S144" s="13" t="n"/>
@@ -10030,7 +10030,7 @@
         <v>0</v>
       </c>
       <c r="Q145" s="12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="R145" s="13" t="n"/>
       <c r="S145" s="13" t="n"/>
@@ -10095,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="Q146" s="12" t="n">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="R146" s="13" t="n"/>
       <c r="S146" s="13" t="n"/>
@@ -10160,7 +10160,7 @@
         <v>0</v>
       </c>
       <c r="Q147" s="12" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="R147" s="13" t="n"/>
       <c r="S147" s="13" t="n"/>
@@ -10225,7 +10225,7 @@
         <v>0</v>
       </c>
       <c r="Q148" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R148" s="13" t="n"/>
       <c r="S148" s="13" t="n"/>
@@ -10290,7 +10290,7 @@
         <v>0</v>
       </c>
       <c r="Q149" s="12" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="R149" s="13" t="n"/>
       <c r="S149" s="13" t="n"/>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q150" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R150" s="13" t="n"/>
       <c r="S150" s="13" t="n"/>
@@ -10420,7 +10420,7 @@
         <v>0</v>
       </c>
       <c r="Q151" s="12" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="R151" s="13" t="n"/>
       <c r="S151" s="13" t="n"/>
@@ -10485,7 +10485,7 @@
         <v>0</v>
       </c>
       <c r="Q152" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R152" s="13" t="n"/>
       <c r="S152" s="13" t="n"/>
@@ -10550,7 +10550,7 @@
         <v>0</v>
       </c>
       <c r="Q153" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R153" s="13" t="n"/>
       <c r="S153" s="13" t="n"/>
@@ -10615,7 +10615,7 @@
         <v>0</v>
       </c>
       <c r="Q154" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R154" s="13" t="n"/>
       <c r="S154" s="13" t="n"/>
@@ -10680,7 +10680,7 @@
         <v>0</v>
       </c>
       <c r="Q155" s="12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R155" s="13" t="n"/>
       <c r="S155" s="13" t="n"/>
@@ -10745,7 +10745,7 @@
         <v>0</v>
       </c>
       <c r="Q156" s="12" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="R156" s="13" t="n"/>
       <c r="S156" s="13" t="n"/>
@@ -10810,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="Q157" s="12" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="R157" s="13" t="n"/>
       <c r="S157" s="13" t="n"/>
@@ -10875,7 +10875,7 @@
         <v>0</v>
       </c>
       <c r="Q158" s="12" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="R158" s="13" t="n"/>
       <c r="S158" s="13" t="n"/>
@@ -10940,7 +10940,7 @@
         <v>0</v>
       </c>
       <c r="Q159" s="12" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="R159" s="13" t="n"/>
       <c r="S159" s="13" t="n"/>
@@ -11005,7 +11005,7 @@
         <v>0</v>
       </c>
       <c r="Q160" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="R160" s="13" t="n"/>
       <c r="S160" s="13" t="n"/>
@@ -11070,7 +11070,7 @@
         <v>0</v>
       </c>
       <c r="Q161" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R161" s="13" t="n"/>
       <c r="S161" s="13" t="n"/>
@@ -11135,7 +11135,7 @@
         <v>0</v>
       </c>
       <c r="Q162" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R162" s="13" t="n"/>
       <c r="S162" s="13" t="n"/>
@@ -11200,7 +11200,7 @@
         <v>0</v>
       </c>
       <c r="Q163" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R163" s="13" t="n"/>
       <c r="S163" s="13" t="n"/>
@@ -11265,7 +11265,7 @@
         <v>0</v>
       </c>
       <c r="Q164" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R164" s="13" t="n"/>
       <c r="S164" s="13" t="n"/>
@@ -11318,7 +11318,7 @@
         <v>0</v>
       </c>
       <c r="M165" s="10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N165" s="10" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
         <v>0</v>
       </c>
       <c r="Q165" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R165" s="13" t="n"/>
       <c r="S165" s="13" t="n"/>
@@ -11395,7 +11395,7 @@
         <v>0</v>
       </c>
       <c r="Q166" s="12" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="R166" s="13" t="n"/>
       <c r="S166" s="13" t="n"/>
@@ -11460,7 +11460,7 @@
         <v>0</v>
       </c>
       <c r="Q167" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R167" s="13" t="n"/>
       <c r="S167" s="13" t="n"/>
@@ -11525,7 +11525,7 @@
         <v>0</v>
       </c>
       <c r="Q168" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="R168" s="13" t="n"/>
       <c r="S168" s="13" t="n"/>
@@ -11578,7 +11578,7 @@
         <v>0</v>
       </c>
       <c r="M169" s="10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N169" s="10" t="n">
         <v>0</v>
@@ -11590,7 +11590,7 @@
         <v>0</v>
       </c>
       <c r="Q169" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R169" s="13" t="n"/>
       <c r="S169" s="13" t="n"/>
@@ -11655,7 +11655,7 @@
         <v>0</v>
       </c>
       <c r="Q170" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="R170" s="13" t="n"/>
       <c r="S170" s="13" t="n"/>
@@ -11720,7 +11720,7 @@
         <v>0</v>
       </c>
       <c r="Q171" s="12" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R171" s="13" t="n"/>
       <c r="S171" s="13" t="n"/>
@@ -11785,7 +11785,7 @@
         <v>0</v>
       </c>
       <c r="Q172" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R172" s="13" t="n"/>
       <c r="S172" s="13" t="n"/>
@@ -11915,7 +11915,7 @@
         <v>0</v>
       </c>
       <c r="Q174" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="R174" s="13" t="n"/>
       <c r="S174" s="13" t="n"/>
@@ -11980,7 +11980,7 @@
         <v>0</v>
       </c>
       <c r="Q175" s="12" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="R175" s="13" t="n"/>
       <c r="S175" s="13" t="n"/>
@@ -12045,7 +12045,7 @@
         <v>0</v>
       </c>
       <c r="Q176" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="R176" s="13" t="n"/>
       <c r="S176" s="13" t="n"/>
@@ -12110,7 +12110,7 @@
         <v>0</v>
       </c>
       <c r="Q177" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="R177" s="13" t="n"/>
       <c r="S177" s="13" t="n"/>
@@ -12175,7 +12175,7 @@
         <v>0</v>
       </c>
       <c r="Q178" s="12" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="R178" s="13" t="n"/>
       <c r="S178" s="13" t="n"/>
@@ -12240,7 +12240,7 @@
         <v>0</v>
       </c>
       <c r="Q179" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="R179" s="13" t="n"/>
       <c r="S179" s="13" t="n"/>
@@ -12305,7 +12305,7 @@
         <v>0</v>
       </c>
       <c r="Q180" s="12" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="R180" s="13" t="n"/>
       <c r="S180" s="13" t="n"/>
@@ -12370,7 +12370,7 @@
         <v>0</v>
       </c>
       <c r="Q181" s="12" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="R181" s="13" t="n"/>
       <c r="S181" s="13" t="n"/>
@@ -12435,7 +12435,7 @@
         <v>0</v>
       </c>
       <c r="Q182" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="R182" s="13" t="n"/>
       <c r="S182" s="13" t="n"/>
@@ -12500,7 +12500,7 @@
         <v>0</v>
       </c>
       <c r="Q183" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="R183" s="13" t="n"/>
       <c r="S183" s="13" t="n"/>
@@ -12565,7 +12565,7 @@
         <v>0</v>
       </c>
       <c r="Q184" s="12" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="R184" s="13" t="n"/>
       <c r="S184" s="13" t="n"/>
@@ -12630,7 +12630,7 @@
         <v>0</v>
       </c>
       <c r="Q185" s="12" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="R185" s="13" t="n"/>
       <c r="S185" s="13" t="n"/>
@@ -12695,7 +12695,7 @@
         <v>0</v>
       </c>
       <c r="Q186" s="12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R186" s="13" t="n"/>
       <c r="S186" s="13" t="n"/>
@@ -12760,7 +12760,7 @@
         <v>0</v>
       </c>
       <c r="Q187" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R187" s="13" t="n"/>
       <c r="S187" s="13" t="n"/>
@@ -12825,7 +12825,7 @@
         <v>0</v>
       </c>
       <c r="Q188" s="12" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="R188" s="13" t="n"/>
       <c r="S188" s="13" t="n"/>
@@ -12890,7 +12890,7 @@
         <v>0</v>
       </c>
       <c r="Q189" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R189" s="13" t="n"/>
       <c r="S189" s="13" t="n"/>
@@ -12955,7 +12955,7 @@
         <v>0</v>
       </c>
       <c r="Q190" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R190" s="13" t="n"/>
       <c r="S190" s="13" t="n"/>
@@ -13020,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="Q191" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R191" s="13" t="n"/>
       <c r="S191" s="13" t="n"/>
@@ -13085,7 +13085,7 @@
         <v>0</v>
       </c>
       <c r="Q192" s="12" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="R192" s="13" t="n"/>
       <c r="S192" s="13" t="n"/>
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="Q193" s="12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="R193" s="13" t="n"/>
       <c r="S193" s="13" t="n"/>
@@ -13215,7 +13215,7 @@
         <v>0</v>
       </c>
       <c r="Q194" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R194" s="13" t="n"/>
       <c r="S194" s="13" t="n"/>
@@ -13280,7 +13280,7 @@
         <v>0</v>
       </c>
       <c r="Q195" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R195" s="13" t="n"/>
       <c r="S195" s="13" t="n"/>
@@ -13345,7 +13345,7 @@
         <v>0</v>
       </c>
       <c r="Q196" s="12" t="n">
-        <v>784</v>
+        <v>0</v>
       </c>
       <c r="R196" s="13" t="n"/>
       <c r="S196" s="13" t="n"/>
@@ -13410,7 +13410,7 @@
         <v>0</v>
       </c>
       <c r="Q197" s="12" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="R197" s="13" t="n"/>
       <c r="S197" s="13" t="n"/>
@@ -13475,7 +13475,7 @@
         <v>0</v>
       </c>
       <c r="Q198" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R198" s="13" t="n"/>
       <c r="S198" s="13" t="n"/>
@@ -13540,7 +13540,7 @@
         <v>0</v>
       </c>
       <c r="Q199" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R199" s="13" t="n"/>
       <c r="S199" s="13" t="n"/>
@@ -13605,7 +13605,7 @@
         <v>0</v>
       </c>
       <c r="Q200" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R200" s="13" t="n"/>
       <c r="S200" s="13" t="n"/>
@@ -13670,7 +13670,7 @@
         <v>0</v>
       </c>
       <c r="Q201" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="R201" s="13" t="n"/>
       <c r="S201" s="13" t="n"/>
@@ -13735,7 +13735,7 @@
         <v>0</v>
       </c>
       <c r="Q202" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="R202" s="13" t="n"/>
       <c r="S202" s="13" t="n"/>
@@ -13800,7 +13800,7 @@
         <v>0</v>
       </c>
       <c r="Q203" s="12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="R203" s="13" t="n"/>
       <c r="S203" s="13" t="n"/>
@@ -13865,7 +13865,7 @@
         <v>0</v>
       </c>
       <c r="Q204" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R204" s="13" t="n"/>
       <c r="S204" s="13" t="n"/>
@@ -13930,7 +13930,7 @@
         <v>0</v>
       </c>
       <c r="Q205" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R205" s="13" t="n"/>
       <c r="S205" s="13" t="n"/>
@@ -13995,7 +13995,7 @@
         <v>0</v>
       </c>
       <c r="Q206" s="12" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="R206" s="13" t="n"/>
       <c r="S206" s="13" t="n"/>
@@ -14060,7 +14060,7 @@
         <v>0</v>
       </c>
       <c r="Q207" s="12" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="R207" s="13" t="n"/>
       <c r="S207" s="13" t="n"/>
@@ -14125,7 +14125,7 @@
         <v>0</v>
       </c>
       <c r="Q208" s="12" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="R208" s="13" t="n"/>
       <c r="S208" s="13" t="n"/>
@@ -14190,7 +14190,7 @@
         <v>0</v>
       </c>
       <c r="Q209" s="12" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="R209" s="13" t="n"/>
       <c r="S209" s="13" t="n"/>
@@ -14255,7 +14255,7 @@
         <v>0</v>
       </c>
       <c r="Q210" s="12" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="R210" s="13" t="n"/>
       <c r="S210" s="13" t="n"/>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="Q211" s="12" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="R211" s="13" t="n"/>
       <c r="S211" s="13" t="n"/>
@@ -14385,7 +14385,7 @@
         <v>0</v>
       </c>
       <c r="Q212" s="12" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="R212" s="13" t="n"/>
       <c r="S212" s="13" t="n"/>
@@ -14450,7 +14450,7 @@
         <v>0</v>
       </c>
       <c r="Q213" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R213" s="13" t="n"/>
       <c r="S213" s="13" t="n"/>
@@ -14515,7 +14515,7 @@
         <v>0</v>
       </c>
       <c r="Q214" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R214" s="13" t="n"/>
       <c r="S214" s="13" t="n"/>
@@ -14580,7 +14580,7 @@
         <v>0</v>
       </c>
       <c r="Q215" s="12" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="R215" s="13" t="n"/>
       <c r="S215" s="13" t="n"/>
@@ -14645,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="Q216" s="12" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="R216" s="13" t="n"/>
       <c r="S216" s="13" t="n"/>
@@ -14710,7 +14710,7 @@
         <v>0</v>
       </c>
       <c r="Q217" s="12" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="R217" s="13" t="n"/>
       <c r="S217" s="13" t="n"/>
@@ -14775,7 +14775,7 @@
         <v>0</v>
       </c>
       <c r="Q218" s="12" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="R218" s="13" t="n"/>
       <c r="S218" s="13" t="n"/>
@@ -14840,7 +14840,7 @@
         <v>0</v>
       </c>
       <c r="Q219" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R219" s="13" t="n"/>
       <c r="S219" s="13" t="n"/>
@@ -14905,7 +14905,7 @@
         <v>0</v>
       </c>
       <c r="Q220" s="12" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="R220" s="13" t="n"/>
       <c r="S220" s="13" t="n"/>
@@ -14970,7 +14970,7 @@
         <v>0</v>
       </c>
       <c r="Q221" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R221" s="13" t="n"/>
       <c r="S221" s="13" t="n"/>
@@ -15035,7 +15035,7 @@
         <v>0</v>
       </c>
       <c r="Q222" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R222" s="13" t="n"/>
       <c r="S222" s="13" t="n"/>
@@ -15100,7 +15100,7 @@
         <v>0</v>
       </c>
       <c r="Q223" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R223" s="13" t="n"/>
       <c r="S223" s="13" t="n"/>
@@ -15165,7 +15165,7 @@
         <v>0</v>
       </c>
       <c r="Q224" s="12" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="R224" s="13" t="n"/>
       <c r="S224" s="13" t="n"/>
@@ -15230,7 +15230,7 @@
         <v>0</v>
       </c>
       <c r="Q225" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="R225" s="13" t="n"/>
       <c r="S225" s="13" t="n"/>
@@ -15295,7 +15295,7 @@
         <v>0</v>
       </c>
       <c r="Q226" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R226" s="13" t="n"/>
       <c r="S226" s="13" t="n"/>
@@ -15360,7 +15360,7 @@
         <v>0</v>
       </c>
       <c r="Q227" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R227" s="13" t="n"/>
       <c r="S227" s="13" t="n"/>
@@ -15425,7 +15425,7 @@
         <v>0</v>
       </c>
       <c r="Q228" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R228" s="13" t="n"/>
       <c r="S228" s="13" t="n"/>
@@ -15490,7 +15490,7 @@
         <v>0</v>
       </c>
       <c r="Q229" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R229" s="13" t="n"/>
       <c r="S229" s="13" t="n"/>
@@ -15543,7 +15543,7 @@
         <v>0</v>
       </c>
       <c r="M230" s="10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N230" s="10" t="n">
         <v>50</v>
@@ -15555,7 +15555,7 @@
         <v>0</v>
       </c>
       <c r="Q230" s="12" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="R230" s="13" t="n"/>
       <c r="S230" s="13" t="n"/>
@@ -15620,7 +15620,7 @@
         <v>0</v>
       </c>
       <c r="Q231" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R231" s="13" t="n"/>
       <c r="S231" s="13" t="n"/>
@@ -15685,7 +15685,7 @@
         <v>0</v>
       </c>
       <c r="Q232" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R232" s="13" t="n"/>
       <c r="S232" s="13" t="n"/>
@@ -15750,7 +15750,7 @@
         <v>0</v>
       </c>
       <c r="Q233" s="12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="R233" s="13" t="n"/>
       <c r="S233" s="13" t="n"/>
@@ -15815,7 +15815,7 @@
         <v>0</v>
       </c>
       <c r="Q234" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R234" s="13" t="n"/>
       <c r="S234" s="13" t="n"/>
@@ -15880,7 +15880,7 @@
         <v>0</v>
       </c>
       <c r="Q235" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R235" s="13" t="n"/>
       <c r="S235" s="13" t="n"/>
@@ -15945,7 +15945,7 @@
         <v>0</v>
       </c>
       <c r="Q236" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R236" s="13" t="n"/>
       <c r="S236" s="13" t="n"/>
@@ -16010,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="Q237" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R237" s="13" t="n"/>
       <c r="S237" s="13" t="n"/>
@@ -16075,7 +16075,7 @@
         <v>0</v>
       </c>
       <c r="Q238" s="12" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="R238" s="13" t="n"/>
       <c r="S238" s="13" t="n"/>
@@ -16140,7 +16140,7 @@
         <v>0</v>
       </c>
       <c r="Q239" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R239" s="13" t="n"/>
       <c r="S239" s="13" t="n"/>
@@ -16205,7 +16205,7 @@
         <v>0</v>
       </c>
       <c r="Q240" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R240" s="13" t="n"/>
       <c r="S240" s="13" t="n"/>
@@ -16270,7 +16270,7 @@
         <v>0</v>
       </c>
       <c r="Q241" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R241" s="13" t="n"/>
       <c r="S241" s="13" t="n"/>
@@ -16335,7 +16335,7 @@
         <v>0</v>
       </c>
       <c r="Q242" s="12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R242" s="13" t="n"/>
       <c r="S242" s="13" t="n"/>
@@ -16400,7 +16400,7 @@
         <v>0</v>
       </c>
       <c r="Q243" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R243" s="13" t="n"/>
       <c r="S243" s="13" t="n"/>
@@ -16465,7 +16465,7 @@
         <v>0</v>
       </c>
       <c r="Q244" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="R244" s="13" t="n"/>
       <c r="S244" s="13" t="n"/>
@@ -16530,7 +16530,7 @@
         <v>0</v>
       </c>
       <c r="Q245" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R245" s="13" t="n"/>
       <c r="S245" s="13" t="n"/>
@@ -16595,7 +16595,7 @@
         <v>0</v>
       </c>
       <c r="Q246" s="12" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="R246" s="13" t="n"/>
       <c r="S246" s="13" t="n"/>
@@ -16660,7 +16660,7 @@
         <v>0</v>
       </c>
       <c r="Q247" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R247" s="13" t="n"/>
       <c r="S247" s="13" t="n"/>
@@ -16725,7 +16725,7 @@
         <v>0</v>
       </c>
       <c r="Q248" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="R248" s="13" t="n"/>
       <c r="S248" s="13" t="n"/>
@@ -16790,7 +16790,7 @@
         <v>0</v>
       </c>
       <c r="Q249" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R249" s="13" t="n"/>
       <c r="S249" s="13" t="n"/>
@@ -16855,7 +16855,7 @@
         <v>0</v>
       </c>
       <c r="Q250" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R250" s="13" t="n"/>
       <c r="S250" s="13" t="n"/>
@@ -16920,7 +16920,7 @@
         <v>0</v>
       </c>
       <c r="Q251" s="12" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="R251" s="13" t="n"/>
       <c r="S251" s="13" t="n"/>
@@ -16985,7 +16985,7 @@
         <v>0</v>
       </c>
       <c r="Q252" s="12" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="R252" s="13" t="n"/>
       <c r="S252" s="13" t="n"/>
@@ -17050,7 +17050,7 @@
         <v>0</v>
       </c>
       <c r="Q253" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="R253" s="13" t="n"/>
       <c r="S253" s="13" t="n"/>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="Q254" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R254" s="13" t="n"/>
       <c r="S254" s="13" t="n"/>
@@ -17180,7 +17180,7 @@
         <v>0</v>
       </c>
       <c r="Q255" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R255" s="13" t="n"/>
       <c r="S255" s="13" t="n"/>
@@ -17245,7 +17245,7 @@
         <v>0</v>
       </c>
       <c r="Q256" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R256" s="13" t="n"/>
       <c r="S256" s="13" t="n"/>
@@ -17310,7 +17310,7 @@
         <v>0</v>
       </c>
       <c r="Q257" s="12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="R257" s="13" t="n"/>
       <c r="S257" s="13" t="n"/>
@@ -17375,7 +17375,7 @@
         <v>0</v>
       </c>
       <c r="Q258" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R258" s="13" t="n"/>
       <c r="S258" s="13" t="n"/>
@@ -17440,7 +17440,7 @@
         <v>0</v>
       </c>
       <c r="Q259" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R259" s="13" t="n"/>
       <c r="S259" s="13" t="n"/>
@@ -17505,7 +17505,7 @@
         <v>0</v>
       </c>
       <c r="Q260" s="12" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="R260" s="13" t="n"/>
       <c r="S260" s="13" t="n"/>
@@ -17570,7 +17570,7 @@
         <v>0</v>
       </c>
       <c r="Q261" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="R261" s="13" t="n"/>
       <c r="S261" s="13" t="n"/>
@@ -17635,7 +17635,7 @@
         <v>0</v>
       </c>
       <c r="Q262" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="R262" s="13" t="n"/>
       <c r="S262" s="13" t="n"/>
@@ -17700,7 +17700,7 @@
         <v>0</v>
       </c>
       <c r="Q263" s="12" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R263" s="13" t="n"/>
       <c r="S263" s="13" t="n"/>
@@ -17765,7 +17765,7 @@
         <v>0</v>
       </c>
       <c r="Q264" s="12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R264" s="13" t="n"/>
       <c r="S264" s="13" t="n"/>
@@ -17830,7 +17830,7 @@
         <v>0</v>
       </c>
       <c r="Q265" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R265" s="13" t="n"/>
       <c r="S265" s="13" t="n"/>
@@ -17895,7 +17895,7 @@
         <v>0</v>
       </c>
       <c r="Q266" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R266" s="13" t="n"/>
       <c r="S266" s="13" t="n"/>
@@ -17960,7 +17960,7 @@
         <v>0</v>
       </c>
       <c r="Q267" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="R267" s="13" t="n"/>
       <c r="S267" s="13" t="n"/>
@@ -18025,7 +18025,7 @@
         <v>0</v>
       </c>
       <c r="Q268" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R268" s="13" t="n"/>
       <c r="S268" s="13" t="n"/>
@@ -18090,7 +18090,7 @@
         <v>0</v>
       </c>
       <c r="Q269" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R269" s="13" t="n"/>
       <c r="S269" s="13" t="n"/>
@@ -18155,7 +18155,7 @@
         <v>0</v>
       </c>
       <c r="Q270" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="R270" s="13" t="n"/>
       <c r="S270" s="13" t="n"/>
@@ -18220,7 +18220,7 @@
         <v>0</v>
       </c>
       <c r="Q271" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R271" s="13" t="n"/>
       <c r="S271" s="13" t="n"/>
@@ -18285,7 +18285,7 @@
         <v>0</v>
       </c>
       <c r="Q272" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="R272" s="13" t="n"/>
       <c r="S272" s="13" t="n"/>
@@ -18350,7 +18350,7 @@
         <v>0</v>
       </c>
       <c r="Q273" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R273" s="13" t="n"/>
       <c r="S273" s="13" t="n"/>
@@ -18415,7 +18415,7 @@
         <v>0</v>
       </c>
       <c r="Q274" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R274" s="13" t="n"/>
       <c r="S274" s="13" t="n"/>
@@ -18480,7 +18480,7 @@
         <v>0</v>
       </c>
       <c r="Q275" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="R275" s="13" t="n"/>
       <c r="S275" s="13" t="n"/>
@@ -18545,7 +18545,7 @@
         <v>0</v>
       </c>
       <c r="Q276" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="R276" s="13" t="n"/>
       <c r="S276" s="13" t="n"/>
@@ -18610,7 +18610,7 @@
         <v>0</v>
       </c>
       <c r="Q277" s="12" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="R277" s="13" t="n"/>
       <c r="S277" s="13" t="n"/>
@@ -18675,7 +18675,7 @@
         <v>0</v>
       </c>
       <c r="Q278" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R278" s="13" t="n"/>
       <c r="S278" s="13" t="n"/>
@@ -18740,7 +18740,7 @@
         <v>0</v>
       </c>
       <c r="Q279" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R279" s="13" t="n"/>
       <c r="S279" s="13" t="n"/>
@@ -18805,7 +18805,7 @@
         <v>0</v>
       </c>
       <c r="Q280" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R280" s="13" t="n"/>
       <c r="S280" s="13" t="n"/>
@@ -18870,7 +18870,7 @@
         <v>0</v>
       </c>
       <c r="Q281" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R281" s="13" t="n"/>
       <c r="S281" s="13" t="n"/>
@@ -18935,7 +18935,7 @@
         <v>0</v>
       </c>
       <c r="Q282" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R282" s="13" t="n"/>
       <c r="S282" s="13" t="n"/>
@@ -19000,7 +19000,7 @@
         <v>0</v>
       </c>
       <c r="Q283" s="12" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="R283" s="13" t="n"/>
       <c r="S283" s="13" t="n"/>
@@ -19065,7 +19065,7 @@
         <v>0</v>
       </c>
       <c r="Q284" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R284" s="13" t="n"/>
       <c r="S284" s="13" t="n"/>
@@ -19130,7 +19130,7 @@
         <v>0</v>
       </c>
       <c r="Q285" s="12" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="R285" s="13" t="n"/>
       <c r="S285" s="13" t="n"/>
@@ -19195,7 +19195,7 @@
         <v>0</v>
       </c>
       <c r="Q286" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R286" s="13" t="n"/>
       <c r="S286" s="13" t="n"/>
@@ -19260,7 +19260,7 @@
         <v>0</v>
       </c>
       <c r="Q287" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="R287" s="13" t="n"/>
       <c r="S287" s="13" t="n"/>
@@ -19325,7 +19325,7 @@
         <v>0</v>
       </c>
       <c r="Q288" s="12" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="R288" s="13" t="n"/>
       <c r="S288" s="13" t="n"/>
@@ -19390,7 +19390,7 @@
         <v>0</v>
       </c>
       <c r="Q289" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R289" s="13" t="n"/>
       <c r="S289" s="13" t="n"/>
@@ -19455,7 +19455,7 @@
         <v>0</v>
       </c>
       <c r="Q290" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R290" s="13" t="n"/>
       <c r="S290" s="13" t="n"/>
@@ -19520,7 +19520,7 @@
         <v>0</v>
       </c>
       <c r="Q291" s="12" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="R291" s="13" t="n"/>
       <c r="S291" s="13" t="n"/>
@@ -19573,7 +19573,7 @@
         <v>0</v>
       </c>
       <c r="M292" s="10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N292" s="10" t="n">
         <v>25</v>
@@ -19585,7 +19585,7 @@
         <v>0</v>
       </c>
       <c r="Q292" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="R292" s="13" t="n"/>
       <c r="S292" s="13" t="n"/>
@@ -19650,7 +19650,7 @@
         <v>0</v>
       </c>
       <c r="Q293" s="12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="R293" s="13" t="n"/>
       <c r="S293" s="13" t="n"/>
@@ -19715,7 +19715,7 @@
         <v>0</v>
       </c>
       <c r="Q294" s="12" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="R294" s="13" t="n"/>
       <c r="S294" s="13" t="n"/>
@@ -19780,7 +19780,7 @@
         <v>0</v>
       </c>
       <c r="Q295" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="R295" s="13" t="n"/>
       <c r="S295" s="13" t="n"/>
@@ -19845,7 +19845,7 @@
         <v>0</v>
       </c>
       <c r="Q296" s="12" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="R296" s="13" t="n"/>
       <c r="S296" s="13" t="n"/>
@@ -19910,7 +19910,7 @@
         <v>0</v>
       </c>
       <c r="Q297" s="12" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="R297" s="13" t="n"/>
       <c r="S297" s="13" t="n"/>
@@ -19975,7 +19975,7 @@
         <v>0</v>
       </c>
       <c r="Q298" s="12" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="R298" s="13" t="n"/>
       <c r="S298" s="13" t="n"/>
@@ -20040,7 +20040,7 @@
         <v>0</v>
       </c>
       <c r="Q299" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="R299" s="13" t="n"/>
       <c r="S299" s="13" t="n"/>
@@ -20105,7 +20105,7 @@
         <v>0</v>
       </c>
       <c r="Q300" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R300" s="13" t="n"/>
       <c r="S300" s="13" t="n"/>
@@ -20170,7 +20170,7 @@
         <v>0</v>
       </c>
       <c r="Q301" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R301" s="13" t="n"/>
       <c r="S301" s="13" t="n"/>
@@ -20217,7 +20217,7 @@
         <v>54</v>
       </c>
       <c r="K302" s="10" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L302" s="10" t="n">
         <v>25</v>
@@ -20235,7 +20235,7 @@
         <v>0</v>
       </c>
       <c r="Q302" s="12" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="R302" s="13" t="n"/>
       <c r="S302" s="13" t="n"/>
@@ -20300,7 +20300,7 @@
         <v>0</v>
       </c>
       <c r="Q303" s="12" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="R303" s="13" t="n"/>
       <c r="S303" s="13" t="n"/>
@@ -20365,7 +20365,7 @@
         <v>0</v>
       </c>
       <c r="Q304" s="12" t="n">
-        <v>787</v>
+        <v>0</v>
       </c>
       <c r="R304" s="13" t="n"/>
       <c r="S304" s="13" t="n"/>
@@ -20430,7 +20430,7 @@
         <v>0</v>
       </c>
       <c r="Q305" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R305" s="13" t="n"/>
       <c r="S305" s="13" t="n"/>
@@ -20495,7 +20495,7 @@
         <v>0</v>
       </c>
       <c r="Q306" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R306" s="13" t="n"/>
       <c r="S306" s="13" t="n"/>
@@ -20560,7 +20560,7 @@
         <v>0</v>
       </c>
       <c r="Q307" s="12" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="R307" s="13" t="n"/>
       <c r="S307" s="13" t="n"/>
@@ -20625,7 +20625,7 @@
         <v>0</v>
       </c>
       <c r="Q308" s="12" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="R308" s="13" t="n"/>
       <c r="S308" s="13" t="n"/>
@@ -20690,7 +20690,7 @@
         <v>0</v>
       </c>
       <c r="Q309" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="R309" s="13" t="n"/>
       <c r="S309" s="13" t="n"/>
@@ -20755,7 +20755,7 @@
         <v>0</v>
       </c>
       <c r="Q310" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R310" s="13" t="n"/>
       <c r="S310" s="13" t="n"/>
@@ -20820,7 +20820,7 @@
         <v>0</v>
       </c>
       <c r="Q311" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R311" s="13" t="n"/>
       <c r="S311" s="13" t="n"/>
@@ -20885,7 +20885,7 @@
         <v>0</v>
       </c>
       <c r="Q312" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R312" s="13" t="n"/>
       <c r="S312" s="13" t="n"/>
@@ -20950,7 +20950,7 @@
         <v>0</v>
       </c>
       <c r="Q313" s="12" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="R313" s="13" t="n"/>
       <c r="S313" s="13" t="n"/>
@@ -21015,7 +21015,7 @@
         <v>0</v>
       </c>
       <c r="Q314" s="12" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="R314" s="13" t="n"/>
       <c r="S314" s="13" t="n"/>
@@ -21080,7 +21080,7 @@
         <v>0</v>
       </c>
       <c r="Q315" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R315" s="13" t="n"/>
       <c r="S315" s="13" t="n"/>
@@ -21145,7 +21145,7 @@
         <v>0</v>
       </c>
       <c r="Q316" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="R316" s="13" t="n"/>
       <c r="S316" s="13" t="n"/>
@@ -21210,7 +21210,7 @@
         <v>0</v>
       </c>
       <c r="Q317" s="12" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="R317" s="13" t="n"/>
       <c r="S317" s="13" t="n"/>
@@ -21275,7 +21275,7 @@
         <v>0</v>
       </c>
       <c r="Q318" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R318" s="13" t="n"/>
       <c r="S318" s="13" t="n"/>
@@ -21340,7 +21340,7 @@
         <v>0</v>
       </c>
       <c r="Q319" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R319" s="13" t="n"/>
       <c r="S319" s="13" t="n"/>
@@ -21405,7 +21405,7 @@
         <v>0</v>
       </c>
       <c r="Q320" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R320" s="13" t="n"/>
       <c r="S320" s="13" t="n"/>
@@ -21470,7 +21470,7 @@
         <v>0</v>
       </c>
       <c r="Q321" s="12" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="R321" s="13" t="n"/>
       <c r="S321" s="13" t="n"/>
@@ -21535,7 +21535,7 @@
         <v>0</v>
       </c>
       <c r="Q322" s="12" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="R322" s="13" t="n"/>
       <c r="S322" s="13" t="n"/>
@@ -21600,7 +21600,7 @@
         <v>0</v>
       </c>
       <c r="Q323" s="12" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="R323" s="13" t="n"/>
       <c r="S323" s="13" t="n"/>
@@ -21665,7 +21665,7 @@
         <v>0</v>
       </c>
       <c r="Q324" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="R324" s="13" t="n"/>
       <c r="S324" s="13" t="n"/>
@@ -21730,7 +21730,7 @@
         <v>0</v>
       </c>
       <c r="Q325" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R325" s="13" t="n"/>
       <c r="S325" s="13" t="n"/>
@@ -21795,7 +21795,7 @@
         <v>0</v>
       </c>
       <c r="Q326" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R326" s="13" t="n"/>
       <c r="S326" s="13" t="n"/>
@@ -21848,7 +21848,7 @@
         <v>0</v>
       </c>
       <c r="M327" s="10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N327" s="10" t="n">
         <v>50</v>
@@ -21860,7 +21860,7 @@
         <v>0</v>
       </c>
       <c r="Q327" s="12" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="R327" s="13" t="n"/>
       <c r="S327" s="13" t="n"/>
@@ -21925,7 +21925,7 @@
         <v>0</v>
       </c>
       <c r="Q328" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R328" s="13" t="n"/>
       <c r="S328" s="13" t="n"/>
@@ -21990,7 +21990,7 @@
         <v>0</v>
       </c>
       <c r="Q329" s="12" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="R329" s="13" t="n"/>
       <c r="S329" s="13" t="n"/>
@@ -22055,7 +22055,7 @@
         <v>0</v>
       </c>
       <c r="Q330" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="R330" s="13" t="n"/>
       <c r="S330" s="13" t="n"/>
@@ -22120,7 +22120,7 @@
         <v>0</v>
       </c>
       <c r="Q331" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R331" s="13" t="n"/>
       <c r="S331" s="13" t="n"/>
@@ -22185,7 +22185,7 @@
         <v>0</v>
       </c>
       <c r="Q332" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R332" s="13" t="n"/>
       <c r="S332" s="13" t="n"/>
@@ -22250,7 +22250,7 @@
         <v>0</v>
       </c>
       <c r="Q333" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R333" s="13" t="n"/>
       <c r="S333" s="13" t="n"/>
@@ -22315,7 +22315,7 @@
         <v>0</v>
       </c>
       <c r="Q334" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="R334" s="13" t="n"/>
       <c r="S334" s="13" t="n"/>
@@ -22380,7 +22380,7 @@
         <v>0</v>
       </c>
       <c r="Q335" s="12" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="R335" s="13" t="n"/>
       <c r="S335" s="13" t="n"/>
@@ -22445,7 +22445,7 @@
         <v>0</v>
       </c>
       <c r="Q336" s="12" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="R336" s="13" t="n"/>
       <c r="S336" s="13" t="n"/>
@@ -22510,7 +22510,7 @@
         <v>0</v>
       </c>
       <c r="Q337" s="12" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="R337" s="13" t="n"/>
       <c r="S337" s="13" t="n"/>
@@ -22575,7 +22575,7 @@
         <v>0</v>
       </c>
       <c r="Q338" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="R338" s="13" t="n"/>
       <c r="S338" s="13" t="n"/>
@@ -22640,7 +22640,7 @@
         <v>0</v>
       </c>
       <c r="Q339" s="12" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="R339" s="13" t="n"/>
       <c r="S339" s="13" t="n"/>
@@ -22705,7 +22705,7 @@
         <v>0</v>
       </c>
       <c r="Q340" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="R340" s="13" t="n"/>
       <c r="S340" s="13" t="n"/>
@@ -22770,7 +22770,7 @@
         <v>0</v>
       </c>
       <c r="Q341" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="R341" s="13" t="n"/>
       <c r="S341" s="13" t="n"/>
@@ -22835,7 +22835,7 @@
         <v>0</v>
       </c>
       <c r="Q342" s="12" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="R342" s="13" t="n"/>
       <c r="S342" s="13" t="n"/>
@@ -22900,7 +22900,7 @@
         <v>0</v>
       </c>
       <c r="Q343" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R343" s="13" t="n"/>
       <c r="S343" s="13" t="n"/>
@@ -22965,7 +22965,7 @@
         <v>0</v>
       </c>
       <c r="Q344" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="R344" s="13" t="n"/>
       <c r="S344" s="13" t="n"/>
@@ -23030,7 +23030,7 @@
         <v>0</v>
       </c>
       <c r="Q345" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R345" s="13" t="n"/>
       <c r="S345" s="13" t="n"/>
@@ -23095,7 +23095,7 @@
         <v>0</v>
       </c>
       <c r="Q346" s="12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R346" s="13" t="n"/>
       <c r="S346" s="13" t="n"/>
@@ -23160,7 +23160,7 @@
         <v>0</v>
       </c>
       <c r="Q347" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R347" s="13" t="n"/>
       <c r="S347" s="13" t="n"/>
@@ -23225,7 +23225,7 @@
         <v>0</v>
       </c>
       <c r="Q348" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R348" s="13" t="n"/>
       <c r="S348" s="13" t="n"/>
@@ -23290,7 +23290,7 @@
         <v>0</v>
       </c>
       <c r="Q349" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R349" s="13" t="n"/>
       <c r="S349" s="13" t="n"/>
@@ -23355,7 +23355,7 @@
         <v>0</v>
       </c>
       <c r="Q350" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="R350" s="13" t="n"/>
       <c r="S350" s="13" t="n"/>
@@ -23420,7 +23420,7 @@
         <v>0</v>
       </c>
       <c r="Q351" s="12" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="R351" s="13" t="n"/>
       <c r="S351" s="13" t="n"/>
@@ -23485,7 +23485,7 @@
         <v>0</v>
       </c>
       <c r="Q352" s="12" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="R352" s="13" t="n"/>
       <c r="S352" s="13" t="n"/>
@@ -23550,7 +23550,7 @@
         <v>0</v>
       </c>
       <c r="Q353" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R353" s="13" t="n"/>
       <c r="S353" s="13" t="n"/>
@@ -23615,7 +23615,7 @@
         <v>0</v>
       </c>
       <c r="Q354" s="12" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="R354" s="13" t="n"/>
       <c r="S354" s="13" t="n"/>
@@ -23680,7 +23680,7 @@
         <v>0</v>
       </c>
       <c r="Q355" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R355" s="13" t="n"/>
       <c r="S355" s="13" t="n"/>
@@ -23745,7 +23745,7 @@
         <v>0</v>
       </c>
       <c r="Q356" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R356" s="13" t="n"/>
       <c r="S356" s="13" t="n"/>
@@ -23810,7 +23810,7 @@
         <v>0</v>
       </c>
       <c r="Q357" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R357" s="13" t="n"/>
       <c r="S357" s="13" t="n"/>
@@ -23875,7 +23875,7 @@
         <v>0</v>
       </c>
       <c r="Q358" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R358" s="13" t="n"/>
       <c r="S358" s="13" t="n"/>
@@ -23940,7 +23940,7 @@
         <v>0</v>
       </c>
       <c r="Q359" s="12" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="R359" s="13" t="n"/>
       <c r="S359" s="13" t="n"/>
@@ -24005,7 +24005,7 @@
         <v>0</v>
       </c>
       <c r="Q360" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="R360" s="13" t="n"/>
       <c r="S360" s="13" t="n"/>
@@ -24070,7 +24070,7 @@
         <v>0</v>
       </c>
       <c r="Q361" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R361" s="13" t="n"/>
       <c r="S361" s="13" t="n"/>
@@ -24135,7 +24135,7 @@
         <v>0</v>
       </c>
       <c r="Q362" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R362" s="13" t="n"/>
       <c r="S362" s="13" t="n"/>
@@ -24200,7 +24200,7 @@
         <v>0</v>
       </c>
       <c r="Q363" s="12" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="R363" s="13" t="n"/>
       <c r="S363" s="13" t="n"/>
@@ -24265,7 +24265,7 @@
         <v>0</v>
       </c>
       <c r="Q364" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="R364" s="13" t="n"/>
       <c r="S364" s="13" t="n"/>
@@ -24330,7 +24330,7 @@
         <v>0</v>
       </c>
       <c r="Q365" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R365" s="13" t="n"/>
       <c r="S365" s="13" t="n"/>
@@ -24395,7 +24395,7 @@
         <v>0</v>
       </c>
       <c r="Q366" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R366" s="13" t="n"/>
       <c r="S366" s="13" t="n"/>
@@ -24460,7 +24460,7 @@
         <v>0</v>
       </c>
       <c r="Q367" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R367" s="13" t="n"/>
       <c r="S367" s="13" t="n"/>
@@ -24525,7 +24525,7 @@
         <v>0</v>
       </c>
       <c r="Q368" s="12" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="R368" s="13" t="n"/>
       <c r="S368" s="13" t="n"/>
@@ -24590,7 +24590,7 @@
         <v>0</v>
       </c>
       <c r="Q369" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R369" s="13" t="n"/>
       <c r="S369" s="13" t="n"/>
@@ -24655,7 +24655,7 @@
         <v>0</v>
       </c>
       <c r="Q370" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R370" s="13" t="n"/>
       <c r="S370" s="13" t="n"/>
@@ -24785,7 +24785,7 @@
         <v>0</v>
       </c>
       <c r="Q372" s="12" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="R372" s="13" t="n"/>
       <c r="S372" s="13" t="n"/>
@@ -24850,7 +24850,7 @@
         <v>0</v>
       </c>
       <c r="Q373" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R373" s="13" t="n"/>
       <c r="S373" s="13" t="n"/>
@@ -24915,7 +24915,7 @@
         <v>0</v>
       </c>
       <c r="Q374" s="12" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="R374" s="13" t="n"/>
       <c r="S374" s="13" t="n"/>
@@ -24980,7 +24980,7 @@
         <v>0</v>
       </c>
       <c r="Q375" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R375" s="13" t="n"/>
       <c r="S375" s="13" t="n"/>
@@ -25045,7 +25045,7 @@
         <v>0</v>
       </c>
       <c r="Q376" s="12" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="R376" s="13" t="n"/>
       <c r="S376" s="13" t="n"/>
@@ -25110,7 +25110,7 @@
         <v>0</v>
       </c>
       <c r="Q377" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R377" s="13" t="n"/>
       <c r="S377" s="13" t="n"/>
@@ -25175,7 +25175,7 @@
         <v>0</v>
       </c>
       <c r="Q378" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="R378" s="13" t="n"/>
       <c r="S378" s="13" t="n"/>
@@ -25240,7 +25240,7 @@
         <v>0</v>
       </c>
       <c r="Q379" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R379" s="13" t="n"/>
       <c r="S379" s="13" t="n"/>
@@ -25305,7 +25305,7 @@
         <v>0</v>
       </c>
       <c r="Q380" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="R380" s="13" t="n"/>
       <c r="S380" s="13" t="n"/>
@@ -25370,7 +25370,7 @@
         <v>0</v>
       </c>
       <c r="Q381" s="12" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="R381" s="13" t="n"/>
       <c r="S381" s="13" t="n"/>
@@ -25435,7 +25435,7 @@
         <v>0</v>
       </c>
       <c r="Q382" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="R382" s="13" t="n"/>
       <c r="S382" s="13" t="n"/>
@@ -25500,7 +25500,7 @@
         <v>0</v>
       </c>
       <c r="Q383" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R383" s="13" t="n"/>
       <c r="S383" s="13" t="n"/>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="Q384" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R384" s="13" t="n"/>
       <c r="S384" s="13" t="n"/>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q385" s="12" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="R385" s="13" t="n"/>
       <c r="S385" s="13" t="n"/>
@@ -25695,7 +25695,7 @@
         <v>0</v>
       </c>
       <c r="Q386" s="12" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="R386" s="13" t="n"/>
       <c r="S386" s="13" t="n"/>
@@ -25760,7 +25760,7 @@
         <v>0</v>
       </c>
       <c r="Q387" s="12" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="R387" s="13" t="n"/>
       <c r="S387" s="13" t="n"/>
@@ -25825,7 +25825,7 @@
         <v>0</v>
       </c>
       <c r="Q388" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="R388" s="13" t="n"/>
       <c r="S388" s="13" t="n"/>
@@ -25878,7 +25878,7 @@
         <v>0</v>
       </c>
       <c r="M389" s="10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N389" s="10" t="n">
         <v>0</v>
@@ -25890,7 +25890,7 @@
         <v>0</v>
       </c>
       <c r="Q389" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R389" s="13" t="n"/>
       <c r="S389" s="13" t="n"/>
@@ -25955,7 +25955,7 @@
         <v>0</v>
       </c>
       <c r="Q390" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R390" s="13" t="n"/>
       <c r="S390" s="13" t="n"/>
@@ -26020,7 +26020,7 @@
         <v>0</v>
       </c>
       <c r="Q391" s="12" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="R391" s="13" t="n"/>
       <c r="S391" s="13" t="n"/>
@@ -26085,7 +26085,7 @@
         <v>0</v>
       </c>
       <c r="Q392" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R392" s="13" t="n"/>
       <c r="S392" s="13" t="n"/>
@@ -26150,7 +26150,7 @@
         <v>0</v>
       </c>
       <c r="Q393" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R393" s="13" t="n"/>
       <c r="S393" s="13" t="n"/>
@@ -26215,7 +26215,7 @@
         <v>0</v>
       </c>
       <c r="Q394" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="R394" s="13" t="n"/>
       <c r="S394" s="13" t="n"/>
@@ -26280,7 +26280,7 @@
         <v>0</v>
       </c>
       <c r="Q395" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R395" s="13" t="n"/>
       <c r="S395" s="13" t="n"/>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="Q396" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="R396" s="13" t="n"/>
       <c r="S396" s="13" t="n"/>
@@ -26410,7 +26410,7 @@
         <v>0</v>
       </c>
       <c r="Q397" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R397" s="13" t="n"/>
       <c r="S397" s="13" t="n"/>
@@ -26475,7 +26475,7 @@
         <v>0</v>
       </c>
       <c r="Q398" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="R398" s="13" t="n"/>
       <c r="S398" s="13" t="n"/>
@@ -26528,7 +26528,7 @@
         <v>0</v>
       </c>
       <c r="M399" s="10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N399" s="10" t="n">
         <v>0</v>
@@ -26540,7 +26540,7 @@
         <v>0</v>
       </c>
       <c r="Q399" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="R399" s="13" t="n"/>
       <c r="S399" s="13" t="n"/>
@@ -26605,7 +26605,7 @@
         <v>0</v>
       </c>
       <c r="Q400" s="12" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="R400" s="13" t="n"/>
       <c r="S400" s="13" t="n"/>
@@ -26670,7 +26670,7 @@
         <v>0</v>
       </c>
       <c r="Q401" s="12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R401" s="13" t="n"/>
       <c r="S401" s="13" t="n"/>
@@ -26735,7 +26735,7 @@
         <v>0</v>
       </c>
       <c r="Q402" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="R402" s="13" t="n"/>
       <c r="S402" s="13" t="n"/>
@@ -26800,7 +26800,7 @@
         <v>0</v>
       </c>
       <c r="Q403" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R403" s="13" t="n"/>
       <c r="S403" s="13" t="n"/>
@@ -26865,7 +26865,7 @@
         <v>0</v>
       </c>
       <c r="Q404" s="12" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="R404" s="13" t="n"/>
       <c r="S404" s="13" t="n"/>
@@ -26930,7 +26930,7 @@
         <v>0</v>
       </c>
       <c r="Q405" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R405" s="13" t="n"/>
       <c r="S405" s="13" t="n"/>
@@ -26995,7 +26995,7 @@
         <v>0</v>
       </c>
       <c r="Q406" s="12" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="R406" s="13" t="n"/>
       <c r="S406" s="13" t="n"/>
@@ -27060,7 +27060,7 @@
         <v>0</v>
       </c>
       <c r="Q407" s="12" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="R407" s="13" t="n"/>
       <c r="S407" s="13" t="n"/>
@@ -27125,7 +27125,7 @@
         <v>0</v>
       </c>
       <c r="Q408" s="12" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="R408" s="13" t="n"/>
       <c r="S408" s="13" t="n"/>
@@ -27190,7 +27190,7 @@
         <v>0</v>
       </c>
       <c r="Q409" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R409" s="13" t="n"/>
       <c r="S409" s="13" t="n"/>
@@ -27255,7 +27255,7 @@
         <v>0</v>
       </c>
       <c r="Q410" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R410" s="13" t="n"/>
       <c r="S410" s="13" t="n"/>
@@ -27320,7 +27320,7 @@
         <v>0</v>
       </c>
       <c r="Q411" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R411" s="13" t="n"/>
       <c r="S411" s="13" t="n"/>
@@ -27385,7 +27385,7 @@
         <v>0</v>
       </c>
       <c r="Q412" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="R412" s="13" t="n"/>
       <c r="S412" s="13" t="n"/>
@@ -27450,7 +27450,7 @@
         <v>0</v>
       </c>
       <c r="Q413" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R413" s="13" t="n"/>
       <c r="S413" s="13" t="n"/>
@@ -27515,7 +27515,7 @@
         <v>0</v>
       </c>
       <c r="Q414" s="12" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="R414" s="13" t="n"/>
       <c r="S414" s="13" t="n"/>
@@ -27580,7 +27580,7 @@
         <v>0</v>
       </c>
       <c r="Q415" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="R415" s="13" t="n"/>
       <c r="S415" s="13" t="n"/>
@@ -27645,7 +27645,7 @@
         <v>0</v>
       </c>
       <c r="Q416" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R416" s="13" t="n"/>
       <c r="S416" s="13" t="n"/>
@@ -27710,7 +27710,7 @@
         <v>0</v>
       </c>
       <c r="Q417" s="12" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="R417" s="13" t="n"/>
       <c r="S417" s="13" t="n"/>
@@ -27775,7 +27775,7 @@
         <v>0</v>
       </c>
       <c r="Q418" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R418" s="13" t="n"/>
       <c r="S418" s="13" t="n"/>
@@ -27840,7 +27840,7 @@
         <v>0</v>
       </c>
       <c r="Q419" s="12" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="R419" s="13" t="n"/>
       <c r="S419" s="13" t="n"/>
@@ -27905,7 +27905,7 @@
         <v>0</v>
       </c>
       <c r="Q420" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="R420" s="13" t="n"/>
       <c r="S420" s="13" t="n"/>
@@ -27970,7 +27970,7 @@
         <v>0</v>
       </c>
       <c r="Q421" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="R421" s="13" t="n"/>
       <c r="S421" s="13" t="n"/>
@@ -28035,7 +28035,7 @@
         <v>0</v>
       </c>
       <c r="Q422" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R422" s="13" t="n"/>
       <c r="S422" s="13" t="n"/>
@@ -28100,7 +28100,7 @@
         <v>0</v>
       </c>
       <c r="Q423" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R423" s="13" t="n"/>
       <c r="S423" s="13" t="n"/>
@@ -28165,7 +28165,7 @@
         <v>0</v>
       </c>
       <c r="Q424" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R424" s="13" t="n"/>
       <c r="S424" s="13" t="n"/>
@@ -28230,7 +28230,7 @@
         <v>0</v>
       </c>
       <c r="Q425" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="R425" s="13" t="n"/>
       <c r="S425" s="13" t="n"/>
@@ -28295,7 +28295,7 @@
         <v>0</v>
       </c>
       <c r="Q426" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R426" s="13" t="n"/>
       <c r="S426" s="13" t="n"/>
@@ -28360,7 +28360,7 @@
         <v>0</v>
       </c>
       <c r="Q427" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R427" s="13" t="n"/>
       <c r="S427" s="13" t="n"/>
@@ -28490,7 +28490,7 @@
         <v>0</v>
       </c>
       <c r="Q429" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R429" s="13" t="n"/>
       <c r="S429" s="13" t="n"/>
@@ -28555,7 +28555,7 @@
         <v>0</v>
       </c>
       <c r="Q430" s="12" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="R430" s="13" t="n"/>
       <c r="S430" s="13" t="n"/>
@@ -28620,7 +28620,7 @@
         <v>0</v>
       </c>
       <c r="Q431" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="R431" s="13" t="n"/>
       <c r="S431" s="13" t="n"/>
@@ -28685,7 +28685,7 @@
         <v>0</v>
       </c>
       <c r="Q432" s="12" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="R432" s="13" t="n"/>
       <c r="S432" s="13" t="n"/>
@@ -28750,7 +28750,7 @@
         <v>0</v>
       </c>
       <c r="Q433" s="12" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="R433" s="13" t="n"/>
       <c r="S433" s="13" t="n"/>
@@ -28815,7 +28815,7 @@
         <v>0</v>
       </c>
       <c r="Q434" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R434" s="13" t="n"/>
       <c r="S434" s="13" t="n"/>
@@ -28880,7 +28880,7 @@
         <v>0</v>
       </c>
       <c r="Q435" s="12" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="R435" s="13" t="n"/>
       <c r="S435" s="13" t="n"/>
@@ -28945,7 +28945,7 @@
         <v>0</v>
       </c>
       <c r="Q436" s="12" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="R436" s="13" t="n"/>
       <c r="S436" s="13" t="n"/>
@@ -29010,7 +29010,7 @@
         <v>0</v>
       </c>
       <c r="Q437" s="12" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="R437" s="13" t="n"/>
       <c r="S437" s="13" t="n"/>
@@ -29075,7 +29075,7 @@
         <v>0</v>
       </c>
       <c r="Q438" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="R438" s="13" t="n"/>
       <c r="S438" s="13" t="n"/>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="Q439" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R439" s="13" t="n"/>
       <c r="S439" s="13" t="n"/>
@@ -29196,7 +29196,7 @@
         <v>0</v>
       </c>
       <c r="N440" s="10" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="O440" s="11" t="n">
         <v>0</v>
@@ -29205,7 +29205,7 @@
         <v>0</v>
       </c>
       <c r="Q440" s="12" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="R440" s="13" t="n"/>
       <c r="S440" s="13" t="n"/>
@@ -29270,7 +29270,7 @@
         <v>0</v>
       </c>
       <c r="Q441" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R441" s="13" t="n"/>
       <c r="S441" s="13" t="n"/>
@@ -29335,7 +29335,7 @@
         <v>0</v>
       </c>
       <c r="Q442" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R442" s="13" t="n"/>
       <c r="S442" s="13" t="n"/>
@@ -29400,7 +29400,7 @@
         <v>0</v>
       </c>
       <c r="Q443" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R443" s="13" t="n"/>
       <c r="S443" s="13" t="n"/>
@@ -29465,7 +29465,7 @@
         <v>0</v>
       </c>
       <c r="Q444" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R444" s="13" t="n"/>
       <c r="S444" s="13" t="n"/>
@@ -29530,7 +29530,7 @@
         <v>0</v>
       </c>
       <c r="Q445" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R445" s="13" t="n"/>
       <c r="S445" s="13" t="n"/>
@@ -29595,7 +29595,7 @@
         <v>0</v>
       </c>
       <c r="Q446" s="12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R446" s="13" t="n"/>
       <c r="S446" s="13" t="n"/>
@@ -29660,7 +29660,7 @@
         <v>0</v>
       </c>
       <c r="Q447" s="12" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="R447" s="13" t="n"/>
       <c r="S447" s="13" t="n"/>
@@ -29725,7 +29725,7 @@
         <v>0</v>
       </c>
       <c r="Q448" s="12" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="R448" s="13" t="n"/>
       <c r="S448" s="13" t="n"/>
@@ -29790,7 +29790,7 @@
         <v>0</v>
       </c>
       <c r="Q449" s="12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="R449" s="13" t="n"/>
       <c r="S449" s="13" t="n"/>
@@ -29855,7 +29855,7 @@
         <v>0</v>
       </c>
       <c r="Q450" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R450" s="13" t="n"/>
       <c r="S450" s="13" t="n"/>
@@ -29920,7 +29920,7 @@
         <v>0</v>
       </c>
       <c r="Q451" s="12" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="R451" s="13" t="n"/>
       <c r="S451" s="13" t="n"/>
@@ -29985,7 +29985,7 @@
         <v>0</v>
       </c>
       <c r="Q452" s="12" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="R452" s="13" t="n"/>
       <c r="S452" s="13" t="n"/>
@@ -30050,7 +30050,7 @@
         <v>0</v>
       </c>
       <c r="Q453" s="12" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="R453" s="13" t="n"/>
       <c r="S453" s="13" t="n"/>
@@ -30115,7 +30115,7 @@
         <v>0</v>
       </c>
       <c r="Q454" s="12" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="R454" s="13" t="n"/>
       <c r="S454" s="13" t="n"/>
@@ -30180,7 +30180,7 @@
         <v>0</v>
       </c>
       <c r="Q455" s="12" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="R455" s="13" t="n"/>
       <c r="S455" s="13" t="n"/>
@@ -30245,7 +30245,7 @@
         <v>0</v>
       </c>
       <c r="Q456" s="12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="R456" s="13" t="n"/>
       <c r="S456" s="13" t="n"/>
@@ -30310,7 +30310,7 @@
         <v>0</v>
       </c>
       <c r="Q457" s="12" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="R457" s="13" t="n"/>
       <c r="S457" s="13" t="n"/>
@@ -30375,7 +30375,7 @@
         <v>0</v>
       </c>
       <c r="Q458" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R458" s="13" t="n"/>
       <c r="S458" s="13" t="n"/>
@@ -30440,7 +30440,7 @@
         <v>0</v>
       </c>
       <c r="Q459" s="12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="R459" s="13" t="n"/>
       <c r="S459" s="13" t="n"/>
@@ -30505,7 +30505,7 @@
         <v>0</v>
       </c>
       <c r="Q460" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R460" s="13" t="n"/>
       <c r="S460" s="13" t="n"/>
@@ -30570,7 +30570,7 @@
         <v>0</v>
       </c>
       <c r="Q461" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R461" s="13" t="n"/>
       <c r="S461" s="13" t="n"/>
@@ -30635,7 +30635,7 @@
         <v>0</v>
       </c>
       <c r="Q462" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R462" s="13" t="n"/>
       <c r="S462" s="13" t="n"/>
@@ -30700,7 +30700,7 @@
         <v>0</v>
       </c>
       <c r="Q463" s="12" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="R463" s="13" t="n"/>
       <c r="S463" s="13" t="n"/>
@@ -30765,7 +30765,7 @@
         <v>0</v>
       </c>
       <c r="Q464" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R464" s="13" t="n"/>
       <c r="S464" s="13" t="n"/>
@@ -30830,7 +30830,7 @@
         <v>0</v>
       </c>
       <c r="Q465" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R465" s="13" t="n"/>
       <c r="S465" s="13" t="n"/>
@@ -30895,7 +30895,7 @@
         <v>0</v>
       </c>
       <c r="Q466" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R466" s="13" t="n"/>
       <c r="S466" s="13" t="n"/>
@@ -30960,7 +30960,7 @@
         <v>0</v>
       </c>
       <c r="Q467" s="12" t="n">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="R467" s="13" t="n"/>
       <c r="S467" s="13" t="n"/>
@@ -31025,7 +31025,7 @@
         <v>0</v>
       </c>
       <c r="Q468" s="12" t="n">
-        <v>411</v>
+        <v>0</v>
       </c>
       <c r="R468" s="13" t="n"/>
       <c r="S468" s="13" t="n"/>
@@ -31090,7 +31090,7 @@
         <v>0</v>
       </c>
       <c r="Q469" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R469" s="13" t="n"/>
       <c r="S469" s="13" t="n"/>
@@ -31155,7 +31155,7 @@
         <v>0</v>
       </c>
       <c r="Q470" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R470" s="13" t="n"/>
       <c r="S470" s="13" t="n"/>
@@ -31220,7 +31220,7 @@
         <v>0</v>
       </c>
       <c r="Q471" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="R471" s="13" t="n"/>
       <c r="S471" s="13" t="n"/>
@@ -31285,7 +31285,7 @@
         <v>0</v>
       </c>
       <c r="Q472" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R472" s="13" t="n"/>
       <c r="S472" s="13" t="n"/>
@@ -31350,7 +31350,7 @@
         <v>0</v>
       </c>
       <c r="Q473" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R473" s="13" t="n"/>
       <c r="S473" s="13" t="n"/>
@@ -31415,7 +31415,7 @@
         <v>0</v>
       </c>
       <c r="Q474" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R474" s="13" t="n"/>
       <c r="S474" s="13" t="n"/>
@@ -31480,7 +31480,7 @@
         <v>0</v>
       </c>
       <c r="Q475" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="R475" s="13" t="n"/>
       <c r="S475" s="13" t="n"/>
@@ -31545,7 +31545,7 @@
         <v>0</v>
       </c>
       <c r="Q476" s="12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="R476" s="13" t="n"/>
       <c r="S476" s="13" t="n"/>
@@ -31610,7 +31610,7 @@
         <v>0</v>
       </c>
       <c r="Q477" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R477" s="13" t="n"/>
       <c r="S477" s="13" t="n"/>
@@ -31675,7 +31675,7 @@
         <v>0</v>
       </c>
       <c r="Q478" s="12" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="R478" s="13" t="n"/>
       <c r="S478" s="13" t="n"/>
@@ -31740,7 +31740,7 @@
         <v>0</v>
       </c>
       <c r="Q479" s="12" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="R479" s="13" t="n"/>
       <c r="S479" s="13" t="n"/>
@@ -31805,7 +31805,7 @@
         <v>0</v>
       </c>
       <c r="Q480" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R480" s="13" t="n"/>
       <c r="S480" s="13" t="n"/>
@@ -31870,7 +31870,7 @@
         <v>0</v>
       </c>
       <c r="Q481" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="R481" s="13" t="n"/>
       <c r="S481" s="13" t="n"/>
@@ -31935,7 +31935,7 @@
         <v>0</v>
       </c>
       <c r="Q482" s="12" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="R482" s="13" t="n"/>
       <c r="S482" s="13" t="n"/>
@@ -32000,7 +32000,7 @@
         <v>0</v>
       </c>
       <c r="Q483" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R483" s="13" t="n"/>
       <c r="S483" s="13" t="n"/>
@@ -32065,7 +32065,7 @@
         <v>0</v>
       </c>
       <c r="Q484" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R484" s="13" t="n"/>
       <c r="S484" s="13" t="n"/>
@@ -32130,7 +32130,7 @@
         <v>0</v>
       </c>
       <c r="Q485" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R485" s="13" t="n"/>
       <c r="S485" s="13" t="n"/>
@@ -32195,7 +32195,7 @@
         <v>0</v>
       </c>
       <c r="Q486" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R486" s="13" t="n"/>
       <c r="S486" s="13" t="n"/>
@@ -32260,7 +32260,7 @@
         <v>0</v>
       </c>
       <c r="Q487" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R487" s="13" t="n"/>
       <c r="S487" s="13" t="n"/>
@@ -32325,7 +32325,7 @@
         <v>0</v>
       </c>
       <c r="Q488" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R488" s="13" t="n"/>
       <c r="S488" s="13" t="n"/>
@@ -32390,7 +32390,7 @@
         <v>0</v>
       </c>
       <c r="Q489" s="12" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="R489" s="13" t="n"/>
       <c r="S489" s="13" t="n"/>
@@ -32455,7 +32455,7 @@
         <v>0</v>
       </c>
       <c r="Q490" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R490" s="13" t="n"/>
       <c r="S490" s="13" t="n"/>
@@ -32520,7 +32520,7 @@
         <v>0</v>
       </c>
       <c r="Q491" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R491" s="13" t="n"/>
       <c r="S491" s="13" t="n"/>
@@ -32585,7 +32585,7 @@
         <v>0</v>
       </c>
       <c r="Q492" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R492" s="13" t="n"/>
       <c r="S492" s="13" t="n"/>
@@ -32650,7 +32650,7 @@
         <v>0</v>
       </c>
       <c r="Q493" s="12" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="R493" s="13" t="n"/>
       <c r="S493" s="13" t="n"/>
@@ -32715,7 +32715,7 @@
         <v>0</v>
       </c>
       <c r="Q494" s="12" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="R494" s="13" t="n"/>
       <c r="S494" s="13" t="n"/>
@@ -32780,7 +32780,7 @@
         <v>0</v>
       </c>
       <c r="Q495" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="R495" s="13" t="n"/>
       <c r="S495" s="13" t="n"/>
@@ -32845,7 +32845,7 @@
         <v>0</v>
       </c>
       <c r="Q496" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R496" s="13" t="n"/>
       <c r="S496" s="13" t="n"/>
@@ -32892,7 +32892,7 @@
         <v>8</v>
       </c>
       <c r="K497" s="10" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L497" s="10" t="n">
         <v>0</v>
@@ -32910,7 +32910,7 @@
         <v>0</v>
       </c>
       <c r="Q497" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R497" s="13" t="n"/>
       <c r="S497" s="13" t="n"/>
@@ -32975,7 +32975,7 @@
         <v>0</v>
       </c>
       <c r="Q498" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R498" s="13" t="n"/>
       <c r="S498" s="13" t="n"/>
@@ -33040,7 +33040,7 @@
         <v>0</v>
       </c>
       <c r="Q499" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="R499" s="13" t="n"/>
       <c r="S499" s="13" t="n"/>
@@ -33105,7 +33105,7 @@
         <v>0</v>
       </c>
       <c r="Q500" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="R500" s="13" t="n"/>
       <c r="S500" s="13" t="n"/>
@@ -33170,7 +33170,7 @@
         <v>0</v>
       </c>
       <c r="Q501" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R501" s="13" t="n"/>
       <c r="S501" s="13" t="n"/>
@@ -33235,7 +33235,7 @@
         <v>0</v>
       </c>
       <c r="Q502" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R502" s="13" t="n"/>
       <c r="S502" s="13" t="n"/>
@@ -33300,7 +33300,7 @@
         <v>0</v>
       </c>
       <c r="Q503" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="R503" s="13" t="n"/>
       <c r="S503" s="13" t="n"/>
@@ -33365,7 +33365,7 @@
         <v>0</v>
       </c>
       <c r="Q504" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R504" s="13" t="n"/>
       <c r="S504" s="13" t="n"/>
@@ -33430,7 +33430,7 @@
         <v>0</v>
       </c>
       <c r="Q505" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="R505" s="13" t="n"/>
       <c r="S505" s="13" t="n"/>
@@ -33495,7 +33495,7 @@
         <v>0</v>
       </c>
       <c r="Q506" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R506" s="13" t="n"/>
       <c r="S506" s="13" t="n"/>
@@ -33560,7 +33560,7 @@
         <v>0</v>
       </c>
       <c r="Q507" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R507" s="13" t="n"/>
       <c r="S507" s="13" t="n"/>
@@ -33625,7 +33625,7 @@
         <v>0</v>
       </c>
       <c r="Q508" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R508" s="13" t="n"/>
       <c r="S508" s="13" t="n"/>
@@ -33690,7 +33690,7 @@
         <v>0</v>
       </c>
       <c r="Q509" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R509" s="13" t="n"/>
       <c r="S509" s="13" t="n"/>
@@ -33740,7 +33740,7 @@
         <v>0</v>
       </c>
       <c r="L510" s="10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M510" s="10" t="n">
         <v>50</v>
@@ -33755,7 +33755,7 @@
         <v>0</v>
       </c>
       <c r="Q510" s="12" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="R510" s="13" t="n"/>
       <c r="S510" s="13" t="n"/>
@@ -33820,7 +33820,7 @@
         <v>0</v>
       </c>
       <c r="Q511" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="R511" s="13" t="n"/>
       <c r="S511" s="13" t="n"/>
@@ -33885,7 +33885,7 @@
         <v>0</v>
       </c>
       <c r="Q512" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="R512" s="13" t="n"/>
       <c r="S512" s="13" t="n"/>
@@ -33950,7 +33950,7 @@
         <v>0</v>
       </c>
       <c r="Q513" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R513" s="13" t="n"/>
       <c r="S513" s="13" t="n"/>
@@ -34015,7 +34015,7 @@
         <v>0</v>
       </c>
       <c r="Q514" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R514" s="13" t="n"/>
       <c r="S514" s="13" t="n"/>
@@ -34080,7 +34080,7 @@
         <v>0</v>
       </c>
       <c r="Q515" s="12" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="R515" s="13" t="n"/>
       <c r="S515" s="13" t="n"/>
@@ -34145,7 +34145,7 @@
         <v>0</v>
       </c>
       <c r="Q516" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R516" s="13" t="n"/>
       <c r="S516" s="13" t="n"/>
@@ -34210,7 +34210,7 @@
         <v>0</v>
       </c>
       <c r="Q517" s="12" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="R517" s="13" t="n"/>
       <c r="S517" s="13" t="n"/>
@@ -34275,7 +34275,7 @@
         <v>0</v>
       </c>
       <c r="Q518" s="12" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="R518" s="13" t="n"/>
       <c r="S518" s="13" t="n"/>
@@ -34340,7 +34340,7 @@
         <v>0</v>
       </c>
       <c r="Q519" s="12" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="R519" s="13" t="n"/>
       <c r="S519" s="13" t="n"/>
@@ -34405,7 +34405,7 @@
         <v>0</v>
       </c>
       <c r="Q520" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="R520" s="13" t="n"/>
       <c r="S520" s="13" t="n"/>
@@ -34470,7 +34470,7 @@
         <v>0</v>
       </c>
       <c r="Q521" s="12" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="R521" s="13" t="n"/>
       <c r="S521" s="13" t="n"/>
@@ -34535,7 +34535,7 @@
         <v>0</v>
       </c>
       <c r="Q522" s="12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R522" s="13" t="n"/>
       <c r="S522" s="13" t="n"/>
@@ -34730,7 +34730,7 @@
         <v>0</v>
       </c>
       <c r="Q525" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R525" s="13" t="n"/>
       <c r="S525" s="13" t="n"/>
@@ -34795,7 +34795,7 @@
         <v>0</v>
       </c>
       <c r="Q526" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R526" s="13" t="n"/>
       <c r="S526" s="13" t="n"/>
@@ -34860,7 +34860,7 @@
         <v>0</v>
       </c>
       <c r="Q527" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R527" s="13" t="n"/>
       <c r="S527" s="13" t="n"/>
@@ -34925,7 +34925,7 @@
         <v>0</v>
       </c>
       <c r="Q528" s="12" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="R528" s="13" t="n"/>
       <c r="S528" s="13" t="n"/>
@@ -34990,7 +34990,7 @@
         <v>0</v>
       </c>
       <c r="Q529" s="12" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="R529" s="13" t="n"/>
       <c r="S529" s="13" t="n"/>
@@ -35055,7 +35055,7 @@
         <v>0</v>
       </c>
       <c r="Q530" s="12" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="R530" s="13" t="n"/>
       <c r="S530" s="13" t="n"/>
@@ -35120,7 +35120,7 @@
         <v>0</v>
       </c>
       <c r="Q531" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R531" s="13" t="n"/>
       <c r="S531" s="13" t="n"/>
@@ -35185,7 +35185,7 @@
         <v>0</v>
       </c>
       <c r="Q532" s="12" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="R532" s="13" t="n"/>
       <c r="S532" s="13" t="n"/>
@@ -35250,7 +35250,7 @@
         <v>0</v>
       </c>
       <c r="Q533" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R533" s="13" t="n"/>
       <c r="S533" s="13" t="n"/>
@@ -35315,7 +35315,7 @@
         <v>0</v>
       </c>
       <c r="Q534" s="12" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="R534" s="13" t="n"/>
       <c r="S534" s="13" t="n"/>
@@ -35368,7 +35368,7 @@
         <v>0</v>
       </c>
       <c r="M535" s="10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N535" s="10" t="n">
         <v>75</v>
@@ -35380,7 +35380,7 @@
         <v>0</v>
       </c>
       <c r="Q535" s="12" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="R535" s="13" t="n"/>
       <c r="S535" s="13" t="n"/>
@@ -35445,7 +35445,7 @@
         <v>0</v>
       </c>
       <c r="Q536" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R536" s="13" t="n"/>
       <c r="S536" s="13" t="n"/>
@@ -35483,7 +35483,7 @@
         <v>7</v>
       </c>
       <c r="H537" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I537" s="10" t="n">
         <v>3</v>
@@ -35498,7 +35498,7 @@
         <v>0</v>
       </c>
       <c r="M537" s="10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N537" s="10" t="n">
         <v>0</v>
@@ -35510,7 +35510,7 @@
         <v>0</v>
       </c>
       <c r="Q537" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R537" s="13" t="n"/>
       <c r="S537" s="13" t="n"/>
@@ -35575,7 +35575,7 @@
         <v>0</v>
       </c>
       <c r="Q538" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R538" s="13" t="n"/>
       <c r="S538" s="13" t="n"/>
@@ -35640,7 +35640,7 @@
         <v>0</v>
       </c>
       <c r="Q539" s="12" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="R539" s="13" t="n"/>
       <c r="S539" s="13" t="n"/>
@@ -35705,7 +35705,7 @@
         <v>0</v>
       </c>
       <c r="Q540" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R540" s="13" t="n"/>
       <c r="S540" s="13" t="n"/>
@@ -35770,7 +35770,7 @@
         <v>0</v>
       </c>
       <c r="Q541" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R541" s="13" t="n"/>
       <c r="S541" s="13" t="n"/>
@@ -35835,7 +35835,7 @@
         <v>0</v>
       </c>
       <c r="Q542" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R542" s="13" t="n"/>
       <c r="S542" s="13" t="n"/>
@@ -35888,7 +35888,7 @@
         <v>0</v>
       </c>
       <c r="M543" s="10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N543" s="10" t="n">
         <v>0</v>
@@ -35900,7 +35900,7 @@
         <v>0</v>
       </c>
       <c r="Q543" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R543" s="13" t="n"/>
       <c r="S543" s="13" t="n"/>
@@ -35965,7 +35965,7 @@
         <v>0</v>
       </c>
       <c r="Q544" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R544" s="13" t="n"/>
       <c r="S544" s="13" t="n"/>
@@ -36030,7 +36030,7 @@
         <v>0</v>
       </c>
       <c r="Q545" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R545" s="13" t="n"/>
       <c r="S545" s="13" t="n"/>
@@ -36095,7 +36095,7 @@
         <v>0</v>
       </c>
       <c r="Q546" s="12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R546" s="13" t="n"/>
       <c r="S546" s="13" t="n"/>
@@ -36225,7 +36225,7 @@
         <v>0</v>
       </c>
       <c r="Q548" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R548" s="13" t="n"/>
       <c r="S548" s="13" t="n"/>
@@ -36290,7 +36290,7 @@
         <v>0</v>
       </c>
       <c r="Q549" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R549" s="13" t="n"/>
       <c r="S549" s="13" t="n"/>
@@ -36355,7 +36355,7 @@
         <v>0</v>
       </c>
       <c r="Q550" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R550" s="13" t="n"/>
       <c r="S550" s="13" t="n"/>
@@ -36420,7 +36420,7 @@
         <v>0</v>
       </c>
       <c r="Q551" s="12" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="R551" s="13" t="n"/>
       <c r="S551" s="13" t="n"/>
@@ -36485,7 +36485,7 @@
         <v>0</v>
       </c>
       <c r="Q552" s="12" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="R552" s="13" t="n"/>
       <c r="S552" s="13" t="n"/>
@@ -36529,7 +36529,7 @@
         <v>3</v>
       </c>
       <c r="J553" s="10" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K553" s="10" t="n">
         <v>0</v>
@@ -36550,7 +36550,7 @@
         <v>0</v>
       </c>
       <c r="Q553" s="12" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="R553" s="13" t="n"/>
       <c r="S553" s="13" t="n"/>
@@ -36615,7 +36615,7 @@
         <v>0</v>
       </c>
       <c r="Q554" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="R554" s="13" t="n"/>
       <c r="S554" s="13" t="n"/>
@@ -36680,7 +36680,7 @@
         <v>0</v>
       </c>
       <c r="Q555" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R555" s="13" t="n"/>
       <c r="S555" s="13" t="n"/>
@@ -36745,7 +36745,7 @@
         <v>0</v>
       </c>
       <c r="Q556" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R556" s="13" t="n"/>
       <c r="S556" s="13" t="n"/>
@@ -36875,7 +36875,7 @@
         <v>0</v>
       </c>
       <c r="Q558" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R558" s="13" t="n"/>
       <c r="S558" s="13" t="n"/>
@@ -36940,7 +36940,7 @@
         <v>0</v>
       </c>
       <c r="Q559" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="R559" s="13" t="n"/>
       <c r="S559" s="13" t="n"/>
@@ -36993,7 +36993,7 @@
         <v>0</v>
       </c>
       <c r="M560" s="10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N560" s="10" t="n">
         <v>0</v>
@@ -37005,7 +37005,7 @@
         <v>0</v>
       </c>
       <c r="Q560" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="R560" s="13" t="n"/>
       <c r="S560" s="13" t="n"/>
@@ -37052,7 +37052,7 @@
         <v>8</v>
       </c>
       <c r="K561" s="10" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L561" s="10" t="n">
         <v>0</v>
@@ -37070,7 +37070,7 @@
         <v>0</v>
       </c>
       <c r="Q561" s="12" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="R561" s="13" t="n"/>
       <c r="S561" s="13" t="n"/>
@@ -37117,7 +37117,7 @@
         <v>13</v>
       </c>
       <c r="K562" s="10" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L562" s="10" t="n">
         <v>0</v>
@@ -37135,7 +37135,7 @@
         <v>0</v>
       </c>
       <c r="Q562" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R562" s="13" t="n"/>
       <c r="S562" s="13" t="n"/>
@@ -37200,7 +37200,7 @@
         <v>0</v>
       </c>
       <c r="Q563" s="12" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="R563" s="13" t="n"/>
       <c r="S563" s="13" t="n"/>
@@ -37265,7 +37265,7 @@
         <v>0</v>
       </c>
       <c r="Q564" s="12" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="R564" s="13" t="n"/>
       <c r="S564" s="13" t="n"/>
@@ -37330,7 +37330,7 @@
         <v>0</v>
       </c>
       <c r="Q565" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="R565" s="13" t="n"/>
       <c r="S565" s="13" t="n"/>
@@ -37395,7 +37395,7 @@
         <v>0</v>
       </c>
       <c r="Q566" s="12" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="R566" s="13" t="n"/>
       <c r="S566" s="13" t="n"/>
@@ -37460,7 +37460,7 @@
         <v>0</v>
       </c>
       <c r="Q567" s="12" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="R567" s="13" t="n"/>
       <c r="S567" s="13" t="n"/>
@@ -37525,7 +37525,7 @@
         <v>0</v>
       </c>
       <c r="Q568" s="12" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="R568" s="13" t="n"/>
       <c r="S568" s="13" t="n"/>
@@ -37578,7 +37578,7 @@
         <v>0</v>
       </c>
       <c r="M569" s="10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N569" s="10" t="n">
         <v>0</v>
@@ -37590,7 +37590,7 @@
         <v>0</v>
       </c>
       <c r="Q569" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R569" s="13" t="n"/>
       <c r="S569" s="13" t="n"/>
@@ -37655,7 +37655,7 @@
         <v>0</v>
       </c>
       <c r="Q570" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R570" s="13" t="n"/>
       <c r="S570" s="13" t="n"/>
@@ -37720,7 +37720,7 @@
         <v>0</v>
       </c>
       <c r="Q571" s="12" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="R571" s="13" t="n"/>
       <c r="S571" s="13" t="n"/>
@@ -37785,7 +37785,7 @@
         <v>0</v>
       </c>
       <c r="Q572" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R572" s="13" t="n"/>
       <c r="S572" s="13" t="n"/>
@@ -37850,7 +37850,7 @@
         <v>0</v>
       </c>
       <c r="Q573" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R573" s="13" t="n"/>
       <c r="S573" s="13" t="n"/>
@@ -37915,7 +37915,7 @@
         <v>0</v>
       </c>
       <c r="Q574" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R574" s="13" t="n"/>
       <c r="S574" s="13" t="n"/>
@@ -37980,7 +37980,7 @@
         <v>0</v>
       </c>
       <c r="Q575" s="12" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R575" s="13" t="n"/>
       <c r="S575" s="13" t="n"/>
@@ -38045,7 +38045,7 @@
         <v>0</v>
       </c>
       <c r="Q576" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R576" s="13" t="n"/>
       <c r="S576" s="13" t="n"/>

--- a/shared/planilla_mes/planilla_2026-06.xlsx
+++ b/shared/planilla_mes/planilla_2026-06.xlsx
@@ -4877,7 +4877,7 @@
         <v>29</v>
       </c>
       <c r="K66" s="10" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L66" s="10" t="n">
         <v>25</v>
@@ -5007,7 +5007,7 @@
         <v>17</v>
       </c>
       <c r="K68" s="10" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L68" s="10" t="n">
         <v>0</v>
@@ -5917,7 +5917,7 @@
         <v>8</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L82" s="10" t="n">
         <v>346</v>
@@ -20217,7 +20217,7 @@
         <v>54</v>
       </c>
       <c r="K302" s="10" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L302" s="10" t="n">
         <v>25</v>
@@ -32892,7 +32892,7 @@
         <v>8</v>
       </c>
       <c r="K497" s="10" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L497" s="10" t="n">
         <v>0</v>
@@ -37052,7 +37052,7 @@
         <v>8</v>
       </c>
       <c r="K561" s="10" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L561" s="10" t="n">
         <v>0</v>
@@ -37117,7 +37117,7 @@
         <v>13</v>
       </c>
       <c r="K562" s="10" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L562" s="10" t="n">
         <v>0</v>
